--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B2">
-        <v>5360</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46269.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B3">
-        <v>5300</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46269.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B4">
-        <v>5260</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46269.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B5">
-        <v>5220</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46269.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B6">
-        <v>5200</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46269.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B7">
-        <v>5180</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46269.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B8">
-        <v>5170</v>
+        <v>4750</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46269.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B9">
-        <v>5170</v>
+        <v>4730</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46269.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B10">
-        <v>5180</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46269.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B11">
-        <v>5200</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46269.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B12">
-        <v>5220</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46269.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B13">
-        <v>5240</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46269.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B14">
-        <v>5250</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46269.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B15">
-        <v>5260</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46269.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B16">
-        <v>5280</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46269.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B17">
-        <v>5310</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46269.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B18">
-        <v>5350</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46269.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B19">
-        <v>5390</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46269.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B20">
-        <v>5430</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46269.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B21">
-        <v>5490</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46269.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B22">
-        <v>5550</v>
+        <v>4780</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46269.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B23">
-        <v>5620</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46269.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B24">
-        <v>5700</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46269.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B25">
-        <v>5790</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46269.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B26">
-        <v>5870</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46269.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B27">
-        <v>5940</v>
+        <v>4840</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46269.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B28">
-        <v>6000</v>
+        <v>4840</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46269.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B29">
-        <v>6040</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46269.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B30">
-        <v>6050</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46269.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B31">
-        <v>6040</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46269.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B32">
-        <v>5990</v>
+        <v>4730</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46269.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B33">
-        <v>5910</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46269.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B34">
-        <v>5800</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46269.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B35">
-        <v>5670</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46269.35416666666</v>
+        <v>46278.35416666666</v>
       </c>
       <c r="B36">
-        <v>5530</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46269.36458333334</v>
+        <v>46278.36458333334</v>
       </c>
       <c r="B37">
-        <v>5370</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46269.375</v>
+        <v>46278.375</v>
       </c>
       <c r="B38">
-        <v>5210</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46269.38541666666</v>
+        <v>46278.38541666666</v>
       </c>
       <c r="B39">
-        <v>5050</v>
+        <v>4360</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46269.39583333334</v>
+        <v>46278.39583333334</v>
       </c>
       <c r="B40">
-        <v>4910</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46269.40625</v>
+        <v>46278.40625</v>
       </c>
       <c r="B41">
-        <v>4790</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46269.41666666666</v>
+        <v>46278.41666666666</v>
       </c>
       <c r="B42">
-        <v>4690</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46269.42708333334</v>
+        <v>46278.42708333334</v>
       </c>
       <c r="B43">
-        <v>4620</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46269.4375</v>
+        <v>46278.4375</v>
       </c>
       <c r="B44">
-        <v>4570</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46269.44791666666</v>
+        <v>46278.44791666666</v>
       </c>
       <c r="B45">
-        <v>4540</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46269.45833333334</v>
+        <v>46278.45833333334</v>
       </c>
       <c r="B46">
-        <v>4540</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46269.46875</v>
+        <v>46278.46875</v>
       </c>
       <c r="B47">
-        <v>4550</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46269.47916666666</v>
+        <v>46278.47916666666</v>
       </c>
       <c r="B48">
-        <v>4570</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46269.48958333334</v>
+        <v>46278.48958333334</v>
       </c>
       <c r="B49">
-        <v>4600</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46269.5</v>
+        <v>46278.5</v>
       </c>
       <c r="B50">
-        <v>4630</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46269.51041666666</v>
+        <v>46278.51041666666</v>
       </c>
       <c r="B51">
-        <v>4660</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46269.52083333334</v>
+        <v>46278.52083333334</v>
       </c>
       <c r="B52">
-        <v>4690</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46269.53125</v>
+        <v>46278.53125</v>
       </c>
       <c r="B53">
-        <v>4720</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46269.54166666666</v>
+        <v>46278.54166666666</v>
       </c>
       <c r="B54">
-        <v>4750</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46269.55208333334</v>
+        <v>46278.55208333334</v>
       </c>
       <c r="B55">
-        <v>4770</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46269.5625</v>
+        <v>46278.5625</v>
       </c>
       <c r="B56">
-        <v>4800</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46269.57291666666</v>
+        <v>46278.57291666666</v>
       </c>
       <c r="B57">
-        <v>4820</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46269.58333333334</v>
+        <v>46278.58333333334</v>
       </c>
       <c r="B58">
-        <v>4860</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46269.59375</v>
+        <v>46278.59375</v>
       </c>
       <c r="B59">
-        <v>4900</v>
+        <v>4310</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46269.60416666666</v>
+        <v>46278.60416666666</v>
       </c>
       <c r="B60">
-        <v>4960</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46269.61458333334</v>
+        <v>46278.61458333334</v>
       </c>
       <c r="B61">
-        <v>5030</v>
+        <v>4370</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46269.625</v>
+        <v>46278.625</v>
       </c>
       <c r="B62">
-        <v>5110</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46269.63541666666</v>
+        <v>46278.63541666666</v>
       </c>
       <c r="B63">
-        <v>5200</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46269.64583333334</v>
+        <v>46278.64583333334</v>
       </c>
       <c r="B64">
-        <v>5310</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46269.65625</v>
+        <v>46278.65625</v>
       </c>
       <c r="B65">
-        <v>5420</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46269.66666666666</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="B66">
-        <v>5540</v>
+        <v>4890</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46269.67708333334</v>
+        <v>46278.67708333334</v>
       </c>
       <c r="B67">
-        <v>5670</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46269.6875</v>
+        <v>46278.6875</v>
       </c>
       <c r="B68">
-        <v>5810</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46269.69791666666</v>
+        <v>46278.69791666666</v>
       </c>
       <c r="B69">
-        <v>5950</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46269.70833333334</v>
+        <v>46278.70833333334</v>
       </c>
       <c r="B70">
-        <v>6090</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46269.71875</v>
+        <v>46278.71875</v>
       </c>
       <c r="B71">
-        <v>6230</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46269.72916666666</v>
+        <v>46278.72916666666</v>
       </c>
       <c r="B72">
-        <v>6360</v>
+        <v>5710</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46269.73958333334</v>
+        <v>46278.73958333334</v>
       </c>
       <c r="B73">
-        <v>6480</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46269.75</v>
+        <v>46278.75</v>
       </c>
       <c r="B74">
-        <v>6580</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46269.76041666666</v>
+        <v>46278.76041666666</v>
       </c>
       <c r="B75">
-        <v>6670</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46269.77083333334</v>
+        <v>46278.77083333334</v>
       </c>
       <c r="B76">
-        <v>6760</v>
+        <v>6040</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46269.78125</v>
+        <v>46278.78125</v>
       </c>
       <c r="B77">
-        <v>6850</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46269.79166666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="B78">
-        <v>6900</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46269.80208333334</v>
+        <v>46278.80208333334</v>
       </c>
       <c r="B79">
-        <v>6940</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46269.8125</v>
+        <v>46278.8125</v>
       </c>
       <c r="B80">
-        <v>6970</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46269.82291666666</v>
+        <v>46278.82291666666</v>
       </c>
       <c r="B81">
-        <v>6950</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46269.83333333334</v>
+        <v>46278.83333333334</v>
       </c>
       <c r="B82">
-        <v>6910</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46269.84375</v>
+        <v>46278.84375</v>
       </c>
       <c r="B83">
-        <v>6840</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46269.85416666666</v>
+        <v>46278.85416666666</v>
       </c>
       <c r="B84">
-        <v>6750</v>
+        <v>5930</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46269.86458333334</v>
+        <v>46278.86458333334</v>
       </c>
       <c r="B85">
-        <v>6650</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46269.875</v>
+        <v>46278.875</v>
       </c>
       <c r="B86">
-        <v>6530</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46269.88541666666</v>
+        <v>46278.88541666666</v>
       </c>
       <c r="B87">
-        <v>6400</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46269.89583333334</v>
+        <v>46278.89583333334</v>
       </c>
       <c r="B88">
-        <v>6270</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46269.90625</v>
+        <v>46278.90625</v>
       </c>
       <c r="B89">
-        <v>6150</v>
+        <v>5420</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46269.91666666666</v>
+        <v>46278.91666666666</v>
       </c>
       <c r="B90">
-        <v>6060</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46269.92708333334</v>
+        <v>46278.92708333334</v>
       </c>
       <c r="B91">
-        <v>5940</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46269.9375</v>
+        <v>46278.9375</v>
       </c>
       <c r="B92">
-        <v>5850</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46269.94791666666</v>
+        <v>46278.94791666666</v>
       </c>
       <c r="B93">
-        <v>5750</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46269.95833333334</v>
+        <v>46278.95833333334</v>
       </c>
       <c r="B94">
-        <v>5690</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46269.96875</v>
+        <v>46278.96875</v>
       </c>
       <c r="B95">
-        <v>5650</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46269.97916666666</v>
+        <v>46278.97916666666</v>
       </c>
       <c r="B96">
-        <v>5580</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46269.98958333334</v>
+        <v>46278.98958333334</v>
       </c>
       <c r="B97">
-        <v>5510</v>
+        <v>4780</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46278</v>
+        <v>46283</v>
       </c>
       <c r="B2">
-        <v>4970</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46278.01041666666</v>
+        <v>46283.01041666666</v>
       </c>
       <c r="B3">
-        <v>4910</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46278.02083333334</v>
+        <v>46283.02083333334</v>
       </c>
       <c r="B4">
-        <v>4870</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46278.03125</v>
+        <v>46283.03125</v>
       </c>
       <c r="B5">
-        <v>4830</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46278.04166666666</v>
+        <v>46283.04166666666</v>
       </c>
       <c r="B6">
-        <v>4800</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46278.05208333334</v>
+        <v>46283.05208333334</v>
       </c>
       <c r="B7">
-        <v>4770</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46278.0625</v>
+        <v>46283.0625</v>
       </c>
       <c r="B8">
-        <v>4750</v>
+        <v>4930</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46278.07291666666</v>
+        <v>46283.07291666666</v>
       </c>
       <c r="B9">
-        <v>4730</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46278.08333333334</v>
+        <v>46283.08333333334</v>
       </c>
       <c r="B10">
-        <v>4720</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46278.09375</v>
+        <v>46283.09375</v>
       </c>
       <c r="B11">
-        <v>4710</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46278.10416666666</v>
+        <v>46283.10416666666</v>
       </c>
       <c r="B12">
-        <v>4710</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46278.11458333334</v>
+        <v>46283.11458333334</v>
       </c>
       <c r="B13">
-        <v>4710</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46278.125</v>
+        <v>46283.125</v>
       </c>
       <c r="B14">
-        <v>4700</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46278.13541666666</v>
+        <v>46283.13541666666</v>
       </c>
       <c r="B15">
-        <v>4700</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46278.14583333334</v>
+        <v>46283.14583333334</v>
       </c>
       <c r="B16">
-        <v>4700</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46278.15625</v>
+        <v>46283.15625</v>
       </c>
       <c r="B17">
-        <v>4700</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46278.16666666666</v>
+        <v>46283.16666666666</v>
       </c>
       <c r="B18">
-        <v>4710</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46278.17708333334</v>
+        <v>46283.17708333334</v>
       </c>
       <c r="B19">
-        <v>4720</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46278.1875</v>
+        <v>46283.1875</v>
       </c>
       <c r="B20">
-        <v>4740</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46278.19791666666</v>
+        <v>46283.19791666666</v>
       </c>
       <c r="B21">
-        <v>4760</v>
+        <v>5350</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46278.20833333334</v>
+        <v>46283.20833333334</v>
       </c>
       <c r="B22">
-        <v>4780</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46278.21875</v>
+        <v>46283.21875</v>
       </c>
       <c r="B23">
-        <v>4790</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46278.22916666666</v>
+        <v>46283.22916666666</v>
       </c>
       <c r="B24">
-        <v>4800</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46278.23958333334</v>
+        <v>46283.23958333334</v>
       </c>
       <c r="B25">
-        <v>4820</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46278.25</v>
+        <v>46283.25</v>
       </c>
       <c r="B26">
-        <v>4830</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46278.26041666666</v>
+        <v>46283.26041666666</v>
       </c>
       <c r="B27">
-        <v>4840</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46278.27083333334</v>
+        <v>46283.27083333334</v>
       </c>
       <c r="B28">
-        <v>4840</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46278.28125</v>
+        <v>46283.28125</v>
       </c>
       <c r="B29">
-        <v>4830</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46278.29166666666</v>
+        <v>46283.29166666666</v>
       </c>
       <c r="B30">
-        <v>4800</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46278.30208333334</v>
+        <v>46283.30208333334</v>
       </c>
       <c r="B31">
-        <v>4770</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46278.3125</v>
+        <v>46283.3125</v>
       </c>
       <c r="B32">
-        <v>4730</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46278.32291666666</v>
+        <v>46283.32291666666</v>
       </c>
       <c r="B33">
-        <v>4680</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46278.33333333334</v>
+        <v>46283.33333333334</v>
       </c>
       <c r="B34">
-        <v>4630</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46278.34375</v>
+        <v>46283.34375</v>
       </c>
       <c r="B35">
-        <v>4570</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46278.35416666666</v>
+        <v>46283.35416666666</v>
       </c>
       <c r="B36">
-        <v>4500</v>
+        <v>5730</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46278.36458333334</v>
+        <v>46283.36458333334</v>
       </c>
       <c r="B37">
-        <v>4450</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46278.375</v>
+        <v>46283.375</v>
       </c>
       <c r="B38">
-        <v>4410</v>
+        <v>5450</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46278.38541666666</v>
+        <v>46283.38541666666</v>
       </c>
       <c r="B39">
-        <v>4360</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46278.39583333334</v>
+        <v>46283.39583333334</v>
       </c>
       <c r="B40">
-        <v>4320</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46278.40625</v>
+        <v>46283.40625</v>
       </c>
       <c r="B41">
-        <v>4290</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46278.41666666666</v>
+        <v>46283.41666666666</v>
       </c>
       <c r="B42">
-        <v>4260</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46278.42708333334</v>
+        <v>46283.42708333334</v>
       </c>
       <c r="B43">
-        <v>4240</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46278.4375</v>
+        <v>46283.4375</v>
       </c>
       <c r="B44">
-        <v>4230</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46278.44791666666</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="B45">
-        <v>4220</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46278.45833333334</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="B46">
-        <v>4210</v>
+        <v>4660</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46278.46875</v>
+        <v>46283.46875</v>
       </c>
       <c r="B47">
-        <v>4210</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46278.47916666666</v>
+        <v>46283.47916666666</v>
       </c>
       <c r="B48">
-        <v>4220</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46278.48958333334</v>
+        <v>46283.48958333334</v>
       </c>
       <c r="B49">
-        <v>4220</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46278.5</v>
+        <v>46283.5</v>
       </c>
       <c r="B50">
-        <v>4230</v>
+        <v>4660</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46278.51041666666</v>
+        <v>46283.51041666666</v>
       </c>
       <c r="B51">
-        <v>4240</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46278.52083333334</v>
+        <v>46283.52083333334</v>
       </c>
       <c r="B52">
-        <v>4250</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46278.53125</v>
+        <v>46283.53125</v>
       </c>
       <c r="B53">
-        <v>4260</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46278.54166666666</v>
+        <v>46283.54166666666</v>
       </c>
       <c r="B54">
-        <v>4270</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46278.55208333334</v>
+        <v>46283.55208333334</v>
       </c>
       <c r="B55">
-        <v>4280</v>
+        <v>4850</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46278.5625</v>
+        <v>46283.5625</v>
       </c>
       <c r="B56">
-        <v>4280</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46278.57291666666</v>
+        <v>46283.57291666666</v>
       </c>
       <c r="B57">
-        <v>4290</v>
+        <v>4970</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46278.58333333334</v>
+        <v>46283.58333333334</v>
       </c>
       <c r="B58">
-        <v>4300</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46278.59375</v>
+        <v>46283.59375</v>
       </c>
       <c r="B59">
-        <v>4310</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46278.60416666666</v>
+        <v>46283.60416666666</v>
       </c>
       <c r="B60">
-        <v>4330</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46278.61458333334</v>
+        <v>46283.61458333334</v>
       </c>
       <c r="B61">
-        <v>4370</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46278.625</v>
+        <v>46283.625</v>
       </c>
       <c r="B62">
-        <v>4430</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46278.63541666666</v>
+        <v>46283.63541666666</v>
       </c>
       <c r="B63">
-        <v>4510</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46278.64583333334</v>
+        <v>46283.64583333334</v>
       </c>
       <c r="B64">
-        <v>4610</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46278.65625</v>
+        <v>46283.65625</v>
       </c>
       <c r="B65">
-        <v>4740</v>
+        <v>5610</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46278.66666666666</v>
+        <v>46283.66666666666</v>
       </c>
       <c r="B66">
-        <v>4890</v>
+        <v>5710</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46278.67708333334</v>
+        <v>46283.67708333334</v>
       </c>
       <c r="B67">
-        <v>5040</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46278.6875</v>
+        <v>46283.6875</v>
       </c>
       <c r="B68">
-        <v>5200</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46278.69791666666</v>
+        <v>46283.69791666666</v>
       </c>
       <c r="B69">
-        <v>5340</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46278.70833333334</v>
+        <v>46283.70833333334</v>
       </c>
       <c r="B70">
-        <v>5480</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46278.71875</v>
+        <v>46283.71875</v>
       </c>
       <c r="B71">
-        <v>5600</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46278.72916666666</v>
+        <v>46283.72916666666</v>
       </c>
       <c r="B72">
-        <v>5710</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46278.73958333334</v>
+        <v>46283.73958333334</v>
       </c>
       <c r="B73">
-        <v>5810</v>
+        <v>6510</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46278.75</v>
+        <v>46283.75</v>
       </c>
       <c r="B74">
-        <v>5900</v>
+        <v>6610</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46278.76041666666</v>
+        <v>46283.76041666666</v>
       </c>
       <c r="B75">
-        <v>5980</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46278.77083333334</v>
+        <v>46283.77083333334</v>
       </c>
       <c r="B76">
-        <v>6040</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46278.78125</v>
+        <v>46283.78125</v>
       </c>
       <c r="B77">
-        <v>6080</v>
+        <v>6870</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46278.79166666666</v>
+        <v>46283.79166666666</v>
       </c>
       <c r="B78">
-        <v>6120</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46278.80208333334</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="B79">
-        <v>6140</v>
+        <v>6980</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46278.8125</v>
+        <v>46283.8125</v>
       </c>
       <c r="B80">
-        <v>6140</v>
+        <v>6970</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46278.82291666666</v>
+        <v>46283.82291666666</v>
       </c>
       <c r="B81">
-        <v>6110</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46278.83333333334</v>
+        <v>46283.83333333334</v>
       </c>
       <c r="B82">
-        <v>6060</v>
+        <v>6780</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46278.84375</v>
+        <v>46283.84375</v>
       </c>
       <c r="B83">
-        <v>6000</v>
+        <v>6630</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46278.85416666666</v>
+        <v>46283.85416666666</v>
       </c>
       <c r="B84">
-        <v>5930</v>
+        <v>6540</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46278.86458333334</v>
+        <v>46283.86458333334</v>
       </c>
       <c r="B85">
-        <v>5830</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46278.875</v>
+        <v>46283.875</v>
       </c>
       <c r="B86">
-        <v>5720</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46278.88541666666</v>
+        <v>46283.88541666666</v>
       </c>
       <c r="B87">
-        <v>5610</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46278.89583333334</v>
+        <v>46283.89583333334</v>
       </c>
       <c r="B88">
-        <v>5500</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46278.90625</v>
+        <v>46283.90625</v>
       </c>
       <c r="B89">
-        <v>5420</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46278.91666666666</v>
+        <v>46283.91666666666</v>
       </c>
       <c r="B90">
-        <v>5320</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46278.92708333334</v>
+        <v>46283.92708333334</v>
       </c>
       <c r="B91">
-        <v>5220</v>
+        <v>5650</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46278.9375</v>
+        <v>46283.9375</v>
       </c>
       <c r="B92">
-        <v>5120</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46278.94791666666</v>
+        <v>46283.94791666666</v>
       </c>
       <c r="B93">
-        <v>5000</v>
+        <v>5420</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46278.95833333334</v>
+        <v>46283.95833333334</v>
       </c>
       <c r="B94">
-        <v>4940</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46278.96875</v>
+        <v>46283.96875</v>
       </c>
       <c r="B95">
-        <v>4900</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46278.97916666666</v>
+        <v>46283.97916666666</v>
       </c>
       <c r="B96">
-        <v>4830</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46278.98958333334</v>
+        <v>46283.98958333334</v>
       </c>
       <c r="B97">
-        <v>4780</v>
+        <v>5140</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="B2">
-        <v>5040</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46283.01041666666</v>
+        <v>46285.01041666666</v>
       </c>
       <c r="B3">
-        <v>5010</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46283.02083333334</v>
+        <v>46285.02083333334</v>
       </c>
       <c r="B4">
-        <v>4990</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46283.03125</v>
+        <v>46285.03125</v>
       </c>
       <c r="B5">
-        <v>4960</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46283.04166666666</v>
+        <v>46285.04166666666</v>
       </c>
       <c r="B6">
-        <v>4930</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46283.05208333334</v>
+        <v>46285.05208333334</v>
       </c>
       <c r="B7">
-        <v>4930</v>
+        <v>4480</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46283.0625</v>
+        <v>46285.0625</v>
       </c>
       <c r="B8">
-        <v>4930</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46283.07291666666</v>
+        <v>46285.07291666666</v>
       </c>
       <c r="B9">
-        <v>4940</v>
+        <v>4440</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46283.08333333334</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="B10">
-        <v>5020</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46283.09375</v>
+        <v>46285.09375</v>
       </c>
       <c r="B11">
-        <v>5060</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46283.10416666666</v>
+        <v>46285.10416666666</v>
       </c>
       <c r="B12">
-        <v>5100</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46283.11458333334</v>
+        <v>46285.11458333334</v>
       </c>
       <c r="B13">
-        <v>5140</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46283.125</v>
+        <v>46285.125</v>
       </c>
       <c r="B14">
-        <v>5170</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46283.13541666666</v>
+        <v>46285.13541666666</v>
       </c>
       <c r="B15">
-        <v>5180</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46283.14583333334</v>
+        <v>46285.14583333334</v>
       </c>
       <c r="B16">
-        <v>5180</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46283.15625</v>
+        <v>46285.15625</v>
       </c>
       <c r="B17">
-        <v>5190</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46283.16666666666</v>
+        <v>46285.16666666666</v>
       </c>
       <c r="B18">
-        <v>5210</v>
+        <v>4430</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46283.17708333334</v>
+        <v>46285.17708333334</v>
       </c>
       <c r="B19">
-        <v>5240</v>
+        <v>4440</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46283.1875</v>
+        <v>46285.1875</v>
       </c>
       <c r="B20">
-        <v>5290</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46283.19791666666</v>
+        <v>46285.19791666666</v>
       </c>
       <c r="B21">
-        <v>5350</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46283.20833333334</v>
+        <v>46285.20833333334</v>
       </c>
       <c r="B22">
-        <v>5410</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46283.21875</v>
+        <v>46285.21875</v>
       </c>
       <c r="B23">
-        <v>5510</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46283.22916666666</v>
+        <v>46285.22916666666</v>
       </c>
       <c r="B24">
-        <v>5620</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46283.23958333334</v>
+        <v>46285.23958333334</v>
       </c>
       <c r="B25">
-        <v>5750</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46283.25</v>
+        <v>46285.25</v>
       </c>
       <c r="B26">
-        <v>5960</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46283.26041666666</v>
+        <v>46285.26041666666</v>
       </c>
       <c r="B27">
-        <v>6080</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46283.27083333334</v>
+        <v>46285.27083333334</v>
       </c>
       <c r="B28">
-        <v>6170</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46283.28125</v>
+        <v>46285.28125</v>
       </c>
       <c r="B29">
-        <v>6190</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46283.29166666666</v>
+        <v>46285.29166666666</v>
       </c>
       <c r="B30">
-        <v>6190</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46283.30208333334</v>
+        <v>46285.30208333334</v>
       </c>
       <c r="B31">
-        <v>6190</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46283.3125</v>
+        <v>46285.3125</v>
       </c>
       <c r="B32">
-        <v>6190</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46283.32291666666</v>
+        <v>46285.32291666666</v>
       </c>
       <c r="B33">
-        <v>6140</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46283.33333333334</v>
+        <v>46285.33333333334</v>
       </c>
       <c r="B34">
-        <v>6020</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46283.34375</v>
+        <v>46285.34375</v>
       </c>
       <c r="B35">
-        <v>5870</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46283.35416666666</v>
+        <v>46285.35416666666</v>
       </c>
       <c r="B36">
-        <v>5730</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46283.36458333334</v>
+        <v>46285.36458333334</v>
       </c>
       <c r="B37">
-        <v>5590</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46283.375</v>
+        <v>46285.375</v>
       </c>
       <c r="B38">
-        <v>5450</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46283.38541666666</v>
+        <v>46285.38541666666</v>
       </c>
       <c r="B39">
-        <v>5310</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46283.39583333334</v>
+        <v>46285.39583333334</v>
       </c>
       <c r="B40">
-        <v>5180</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46283.40625</v>
+        <v>46285.40625</v>
       </c>
       <c r="B41">
-        <v>5060</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46283.41666666666</v>
+        <v>46285.41666666666</v>
       </c>
       <c r="B42">
-        <v>4920</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46283.42708333334</v>
+        <v>46285.42708333334</v>
       </c>
       <c r="B43">
-        <v>4820</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46283.4375</v>
+        <v>46285.4375</v>
       </c>
       <c r="B44">
-        <v>4760</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46283.44791666666</v>
+        <v>46285.44791666666</v>
       </c>
       <c r="B45">
-        <v>4710</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46283.45833333334</v>
+        <v>46285.45833333334</v>
       </c>
       <c r="B46">
-        <v>4660</v>
+        <v>3110</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46283.46875</v>
+        <v>46285.46875</v>
       </c>
       <c r="B47">
-        <v>4650</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46283.47916666666</v>
+        <v>46285.47916666666</v>
       </c>
       <c r="B48">
-        <v>4650</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46283.48958333334</v>
+        <v>46285.48958333334</v>
       </c>
       <c r="B49">
-        <v>4650</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46283.5</v>
+        <v>46285.5</v>
       </c>
       <c r="B50">
-        <v>4660</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46283.51041666666</v>
+        <v>46285.51041666666</v>
       </c>
       <c r="B51">
-        <v>4680</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46283.52083333334</v>
+        <v>46285.52083333334</v>
       </c>
       <c r="B52">
-        <v>4710</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46283.53125</v>
+        <v>46285.53125</v>
       </c>
       <c r="B53">
-        <v>4740</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46283.54166666666</v>
+        <v>46285.54166666666</v>
       </c>
       <c r="B54">
-        <v>4790</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46283.55208333334</v>
+        <v>46285.55208333334</v>
       </c>
       <c r="B55">
-        <v>4850</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46283.5625</v>
+        <v>46285.5625</v>
       </c>
       <c r="B56">
-        <v>4900</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46283.57291666666</v>
+        <v>46285.57291666666</v>
       </c>
       <c r="B57">
-        <v>4970</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46283.58333333334</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="B58">
-        <v>5040</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46283.59375</v>
+        <v>46285.59375</v>
       </c>
       <c r="B59">
-        <v>5120</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46283.60416666666</v>
+        <v>46285.60416666666</v>
       </c>
       <c r="B60">
-        <v>5180</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46283.61458333334</v>
+        <v>46285.61458333334</v>
       </c>
       <c r="B61">
-        <v>5260</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46283.625</v>
+        <v>46285.625</v>
       </c>
       <c r="B62">
-        <v>5340</v>
+        <v>3770</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46283.63541666666</v>
+        <v>46285.63541666666</v>
       </c>
       <c r="B63">
-        <v>5430</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46283.64583333334</v>
+        <v>46285.64583333334</v>
       </c>
       <c r="B64">
-        <v>5510</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46283.65625</v>
+        <v>46285.65625</v>
       </c>
       <c r="B65">
-        <v>5610</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46283.66666666666</v>
+        <v>46285.66666666666</v>
       </c>
       <c r="B66">
-        <v>5710</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46283.67708333334</v>
+        <v>46285.67708333334</v>
       </c>
       <c r="B67">
-        <v>5820</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46283.6875</v>
+        <v>46285.6875</v>
       </c>
       <c r="B68">
-        <v>5940</v>
+        <v>4660</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46283.69791666666</v>
+        <v>46285.69791666666</v>
       </c>
       <c r="B69">
-        <v>6050</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46283.70833333334</v>
+        <v>46285.70833333334</v>
       </c>
       <c r="B70">
-        <v>6180</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46283.71875</v>
+        <v>46285.71875</v>
       </c>
       <c r="B71">
-        <v>6290</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46283.72916666666</v>
+        <v>46285.72916666666</v>
       </c>
       <c r="B72">
-        <v>6410</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46283.73958333334</v>
+        <v>46285.73958333334</v>
       </c>
       <c r="B73">
-        <v>6510</v>
+        <v>5420</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46283.75</v>
+        <v>46285.75</v>
       </c>
       <c r="B74">
-        <v>6610</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46283.76041666666</v>
+        <v>46285.76041666666</v>
       </c>
       <c r="B75">
-        <v>6720</v>
+        <v>5690</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46283.77083333334</v>
+        <v>46285.77083333334</v>
       </c>
       <c r="B76">
-        <v>6800</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46283.78125</v>
+        <v>46285.78125</v>
       </c>
       <c r="B77">
-        <v>6870</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46283.79166666666</v>
+        <v>46285.79166666666</v>
       </c>
       <c r="B78">
-        <v>6930</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46283.80208333334</v>
+        <v>46285.80208333334</v>
       </c>
       <c r="B79">
-        <v>6980</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46283.8125</v>
+        <v>46285.8125</v>
       </c>
       <c r="B80">
-        <v>6970</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46283.82291666666</v>
+        <v>46285.82291666666</v>
       </c>
       <c r="B81">
-        <v>6920</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46283.83333333334</v>
+        <v>46285.83333333334</v>
       </c>
       <c r="B82">
-        <v>6780</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46283.84375</v>
+        <v>46285.84375</v>
       </c>
       <c r="B83">
-        <v>6630</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46283.85416666666</v>
+        <v>46285.85416666666</v>
       </c>
       <c r="B84">
-        <v>6540</v>
+        <v>5640</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46283.86458333334</v>
+        <v>46285.86458333334</v>
       </c>
       <c r="B85">
-        <v>6450</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46283.875</v>
+        <v>46285.875</v>
       </c>
       <c r="B86">
-        <v>6290</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46283.88541666666</v>
+        <v>46285.88541666666</v>
       </c>
       <c r="B87">
-        <v>6140</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46283.89583333334</v>
+        <v>46285.89583333334</v>
       </c>
       <c r="B88">
-        <v>5990</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46283.90625</v>
+        <v>46285.90625</v>
       </c>
       <c r="B89">
-        <v>5860</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46283.91666666666</v>
+        <v>46285.91666666666</v>
       </c>
       <c r="B90">
-        <v>5770</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46283.92708333334</v>
+        <v>46285.92708333334</v>
       </c>
       <c r="B91">
-        <v>5650</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46283.9375</v>
+        <v>46285.9375</v>
       </c>
       <c r="B92">
-        <v>5530</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46283.94791666666</v>
+        <v>46285.94791666666</v>
       </c>
       <c r="B93">
-        <v>5420</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46283.95833333334</v>
+        <v>46285.95833333334</v>
       </c>
       <c r="B94">
-        <v>5300</v>
+        <v>4750</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46283.96875</v>
+        <v>46285.96875</v>
       </c>
       <c r="B95">
-        <v>5240</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46283.97916666666</v>
+        <v>46285.97916666666</v>
       </c>
       <c r="B96">
-        <v>5190</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46283.98958333334</v>
+        <v>46285.98958333334</v>
       </c>
       <c r="B97">
-        <v>5140</v>
+        <v>4590</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B2">
-        <v>5150</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46298.01041666666</v>
+        <v>46299.01041666666</v>
       </c>
       <c r="B3">
-        <v>5110</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46298.02083333334</v>
+        <v>46299.02083333334</v>
       </c>
       <c r="B4">
-        <v>5080</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46298.03125</v>
+        <v>46299.03125</v>
       </c>
       <c r="B5">
-        <v>5060</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46298.04166666666</v>
+        <v>46299.04166666666</v>
       </c>
       <c r="B6">
-        <v>5030</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46298.05208333334</v>
+        <v>46299.05208333334</v>
       </c>
       <c r="B7">
-        <v>5010</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46298.0625</v>
+        <v>46299.0625</v>
       </c>
       <c r="B8">
-        <v>4990</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46298.07291666666</v>
+        <v>46299.07291666666</v>
       </c>
       <c r="B9">
-        <v>4970</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46298.08333333334</v>
+        <v>46299.08333333334</v>
       </c>
       <c r="B10">
-        <v>4960</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46298.09375</v>
+        <v>46299.09375</v>
       </c>
       <c r="B11">
-        <v>4950</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46298.10416666666</v>
+        <v>46299.10416666666</v>
       </c>
       <c r="B12">
-        <v>4950</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46298.11458333334</v>
+        <v>46299.11458333334</v>
       </c>
       <c r="B13">
-        <v>4940</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46298.125</v>
+        <v>46299.125</v>
       </c>
       <c r="B14">
-        <v>4940</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46298.13541666666</v>
+        <v>46299.13541666666</v>
       </c>
       <c r="B15">
-        <v>4950</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46298.14583333334</v>
+        <v>46299.14583333334</v>
       </c>
       <c r="B16">
-        <v>4950</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46298.15625</v>
+        <v>46299.15625</v>
       </c>
       <c r="B17">
-        <v>4960</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46298.16666666666</v>
+        <v>46299.16666666666</v>
       </c>
       <c r="B18">
-        <v>4970</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46298.17708333334</v>
+        <v>46299.17708333334</v>
       </c>
       <c r="B19">
-        <v>4990</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46298.1875</v>
+        <v>46299.1875</v>
       </c>
       <c r="B20">
-        <v>5010</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46298.19791666666</v>
+        <v>46299.19791666666</v>
       </c>
       <c r="B21">
-        <v>5030</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46298.20833333334</v>
+        <v>46299.20833333334</v>
       </c>
       <c r="B22">
-        <v>5050</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46298.21875</v>
+        <v>46299.21875</v>
       </c>
       <c r="B23">
-        <v>5080</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46298.22916666666</v>
+        <v>46299.22916666666</v>
       </c>
       <c r="B24">
-        <v>5110</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46298.23958333334</v>
+        <v>46299.23958333334</v>
       </c>
       <c r="B25">
-        <v>5160</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46298.25</v>
+        <v>46299.25</v>
       </c>
       <c r="B26">
-        <v>5210</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46298.26041666666</v>
+        <v>46299.26041666666</v>
       </c>
       <c r="B27">
-        <v>5240</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46298.27083333334</v>
+        <v>46299.27083333334</v>
       </c>
       <c r="B28">
-        <v>5260</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46298.28125</v>
+        <v>46299.28125</v>
       </c>
       <c r="B29">
-        <v>5290</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46298.29166666666</v>
+        <v>46299.29166666666</v>
       </c>
       <c r="B30">
-        <v>5320</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46298.30208333334</v>
+        <v>46299.30208333334</v>
       </c>
       <c r="B31">
-        <v>5310</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46298.3125</v>
+        <v>46299.3125</v>
       </c>
       <c r="B32">
-        <v>5280</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46298.32291666666</v>
+        <v>46299.32291666666</v>
       </c>
       <c r="B33">
-        <v>5210</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46298.33333333334</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="B34">
-        <v>5070</v>
+        <v>4370</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46298.34375</v>
+        <v>46299.34375</v>
       </c>
       <c r="B35">
-        <v>4940</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46298.35416666666</v>
+        <v>46299.35416666666</v>
       </c>
       <c r="B36">
-        <v>4820</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46298.36458333334</v>
+        <v>46299.36458333334</v>
       </c>
       <c r="B37">
-        <v>4690</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46298.375</v>
+        <v>46299.375</v>
       </c>
       <c r="B38">
-        <v>4560</v>
+        <v>3790</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46298.38541666666</v>
+        <v>46299.38541666666</v>
       </c>
       <c r="B39">
-        <v>4430</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46298.39583333334</v>
+        <v>46299.39583333334</v>
       </c>
       <c r="B40">
-        <v>4300</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46298.40625</v>
+        <v>46299.40625</v>
       </c>
       <c r="B41">
-        <v>4190</v>
+        <v>3370</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46298.41666666666</v>
+        <v>46299.41666666666</v>
       </c>
       <c r="B42">
-        <v>4090</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46298.42708333334</v>
+        <v>46299.42708333334</v>
       </c>
       <c r="B43">
-        <v>3990</v>
+        <v>3110</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46298.4375</v>
+        <v>46299.4375</v>
       </c>
       <c r="B44">
-        <v>3910</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46298.44791666666</v>
+        <v>46299.44791666666</v>
       </c>
       <c r="B45">
-        <v>3800</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46298.45833333334</v>
+        <v>46299.45833333334</v>
       </c>
       <c r="B46">
-        <v>3670</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46298.46875</v>
+        <v>46299.46875</v>
       </c>
       <c r="B47">
-        <v>3630</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46298.47916666666</v>
+        <v>46299.47916666666</v>
       </c>
       <c r="B48">
-        <v>3630</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46298.48958333334</v>
+        <v>46299.48958333334</v>
       </c>
       <c r="B49">
-        <v>3670</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46298.5</v>
+        <v>46299.5</v>
       </c>
       <c r="B50">
-        <v>3690</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46298.51041666666</v>
+        <v>46299.51041666666</v>
       </c>
       <c r="B51">
-        <v>3700</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46298.52083333334</v>
+        <v>46299.52083333334</v>
       </c>
       <c r="B52">
-        <v>3700</v>
+        <v>3110</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46298.53125</v>
+        <v>46299.53125</v>
       </c>
       <c r="B53">
-        <v>3710</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46298.54166666666</v>
+        <v>46299.54166666666</v>
       </c>
       <c r="B54">
-        <v>3730</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46298.55208333334</v>
+        <v>46299.55208333334</v>
       </c>
       <c r="B55">
-        <v>3770</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46298.5625</v>
+        <v>46299.5625</v>
       </c>
       <c r="B56">
-        <v>3810</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46298.57291666666</v>
+        <v>46299.57291666666</v>
       </c>
       <c r="B57">
-        <v>3890</v>
+        <v>3390</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46298.58333333334</v>
+        <v>46299.58333333334</v>
       </c>
       <c r="B58">
-        <v>4000</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46298.59375</v>
+        <v>46299.59375</v>
       </c>
       <c r="B59">
-        <v>4090</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46298.60416666666</v>
+        <v>46299.60416666666</v>
       </c>
       <c r="B60">
-        <v>4200</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46298.61458333334</v>
+        <v>46299.61458333334</v>
       </c>
       <c r="B61">
-        <v>4310</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46298.625</v>
+        <v>46299.625</v>
       </c>
       <c r="B62">
-        <v>4410</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46298.63541666666</v>
+        <v>46299.63541666666</v>
       </c>
       <c r="B63">
-        <v>4530</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46298.64583333334</v>
+        <v>46299.64583333334</v>
       </c>
       <c r="B64">
-        <v>4660</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46298.65625</v>
+        <v>46299.65625</v>
       </c>
       <c r="B65">
-        <v>4800</v>
+        <v>4170</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46298.66666666666</v>
+        <v>46299.66666666666</v>
       </c>
       <c r="B66">
-        <v>4950</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46298.67708333334</v>
+        <v>46299.67708333334</v>
       </c>
       <c r="B67">
-        <v>5110</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46298.6875</v>
+        <v>46299.6875</v>
       </c>
       <c r="B68">
-        <v>5280</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46298.69791666666</v>
+        <v>46299.69791666666</v>
       </c>
       <c r="B69">
-        <v>5460</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46298.70833333334</v>
+        <v>46299.70833333334</v>
       </c>
       <c r="B70">
-        <v>5660</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46298.71875</v>
+        <v>46299.71875</v>
       </c>
       <c r="B71">
-        <v>5820</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46298.72916666666</v>
+        <v>46299.72916666666</v>
       </c>
       <c r="B72">
-        <v>5980</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46298.73958333334</v>
+        <v>46299.73958333334</v>
       </c>
       <c r="B73">
-        <v>6140</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46298.75</v>
+        <v>46299.75</v>
       </c>
       <c r="B74">
-        <v>6250</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46298.76041666666</v>
+        <v>46299.76041666666</v>
       </c>
       <c r="B75">
-        <v>6370</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46298.77083333334</v>
+        <v>46299.77083333334</v>
       </c>
       <c r="B76">
-        <v>6460</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46298.78125</v>
+        <v>46299.78125</v>
       </c>
       <c r="B77">
-        <v>6520</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46298.79166666666</v>
+        <v>46299.79166666666</v>
       </c>
       <c r="B78">
-        <v>6570</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46298.80208333334</v>
+        <v>46299.80208333334</v>
       </c>
       <c r="B79">
-        <v>6600</v>
+        <v>6070</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46298.8125</v>
+        <v>46299.8125</v>
       </c>
       <c r="B80">
-        <v>6560</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46298.82291666666</v>
+        <v>46299.82291666666</v>
       </c>
       <c r="B81">
-        <v>6470</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46298.83333333334</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="B82">
-        <v>6310</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46298.84375</v>
+        <v>46299.84375</v>
       </c>
       <c r="B83">
-        <v>6180</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46298.85416666666</v>
+        <v>46299.85416666666</v>
       </c>
       <c r="B84">
-        <v>6020</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46298.86458333334</v>
+        <v>46299.86458333334</v>
       </c>
       <c r="B85">
-        <v>5890</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46298.875</v>
+        <v>46299.875</v>
       </c>
       <c r="B86">
-        <v>5760</v>
+        <v>5420</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46298.88541666666</v>
+        <v>46299.88541666666</v>
       </c>
       <c r="B87">
-        <v>5670</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46298.89583333334</v>
+        <v>46299.89583333334</v>
       </c>
       <c r="B88">
-        <v>5540</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46298.90625</v>
+        <v>46299.90625</v>
       </c>
       <c r="B89">
-        <v>5430</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46298.91666666666</v>
+        <v>46299.91666666666</v>
       </c>
       <c r="B90">
-        <v>5330</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46298.92708333334</v>
+        <v>46299.92708333334</v>
       </c>
       <c r="B91">
-        <v>5240</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46298.9375</v>
+        <v>46299.9375</v>
       </c>
       <c r="B92">
-        <v>5160</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46298.94791666666</v>
+        <v>46299.94791666666</v>
       </c>
       <c r="B93">
-        <v>5070</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46298.95833333334</v>
+        <v>46299.95833333334</v>
       </c>
       <c r="B94">
-        <v>5020</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46298.96875</v>
+        <v>46299.96875</v>
       </c>
       <c r="B95">
-        <v>4980</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46298.97916666666</v>
+        <v>46299.97916666666</v>
       </c>
       <c r="B96">
-        <v>4950</v>
+        <v>4840</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46298.98958333334</v>
+        <v>46299.98958333334</v>
       </c>
       <c r="B97">
-        <v>4890</v>
+        <v>4770</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B2">
-        <v>4820</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46299.01041666666</v>
+        <v>46300.01041666666</v>
       </c>
       <c r="B3">
-        <v>4770</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46299.02083333334</v>
+        <v>46300.02083333334</v>
       </c>
       <c r="B4">
-        <v>4720</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46299.03125</v>
+        <v>46300.03125</v>
       </c>
       <c r="B5">
-        <v>4690</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46299.04166666666</v>
+        <v>46300.04166666666</v>
       </c>
       <c r="B6">
-        <v>4640</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46299.05208333334</v>
+        <v>46300.05208333334</v>
       </c>
       <c r="B7">
-        <v>4610</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46299.0625</v>
+        <v>46300.0625</v>
       </c>
       <c r="B8">
-        <v>4590</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46299.07291666666</v>
+        <v>46300.07291666666</v>
       </c>
       <c r="B9">
-        <v>4560</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46299.08333333334</v>
+        <v>46300.08333333334</v>
       </c>
       <c r="B10">
-        <v>4540</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46299.09375</v>
+        <v>46300.09375</v>
       </c>
       <c r="B11">
-        <v>4530</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46299.10416666666</v>
+        <v>46300.10416666666</v>
       </c>
       <c r="B12">
-        <v>4530</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46299.11458333334</v>
+        <v>46300.11458333334</v>
       </c>
       <c r="B13">
-        <v>4520</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46299.125</v>
+        <v>46300.125</v>
       </c>
       <c r="B14">
-        <v>4500</v>
+        <v>4750</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46299.13541666666</v>
+        <v>46300.13541666666</v>
       </c>
       <c r="B15">
-        <v>4490</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46299.14583333334</v>
+        <v>46300.14583333334</v>
       </c>
       <c r="B16">
-        <v>4500</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46299.15625</v>
+        <v>46300.15625</v>
       </c>
       <c r="B17">
-        <v>4510</v>
+        <v>4890</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46299.16666666666</v>
+        <v>46300.16666666666</v>
       </c>
       <c r="B18">
-        <v>4550</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46299.17708333334</v>
+        <v>46300.17708333334</v>
       </c>
       <c r="B19">
-        <v>4570</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46299.1875</v>
+        <v>46300.1875</v>
       </c>
       <c r="B20">
-        <v>4590</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46299.19791666666</v>
+        <v>46300.19791666666</v>
       </c>
       <c r="B21">
-        <v>4610</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46299.20833333334</v>
+        <v>46300.20833333334</v>
       </c>
       <c r="B22">
-        <v>4650</v>
+        <v>5420</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46299.21875</v>
+        <v>46300.21875</v>
       </c>
       <c r="B23">
-        <v>4670</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46299.22916666666</v>
+        <v>46300.22916666666</v>
       </c>
       <c r="B24">
-        <v>4690</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46299.23958333334</v>
+        <v>46300.23958333334</v>
       </c>
       <c r="B25">
-        <v>4710</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46299.25</v>
+        <v>46300.25</v>
       </c>
       <c r="B26">
-        <v>4740</v>
+        <v>6050</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46299.26041666666</v>
+        <v>46300.26041666666</v>
       </c>
       <c r="B27">
-        <v>4760</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46299.27083333334</v>
+        <v>46300.27083333334</v>
       </c>
       <c r="B28">
-        <v>4760</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46299.28125</v>
+        <v>46300.28125</v>
       </c>
       <c r="B29">
-        <v>4740</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46299.29166666666</v>
+        <v>46300.29166666666</v>
       </c>
       <c r="B30">
-        <v>4720</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46299.30208333334</v>
+        <v>46300.30208333334</v>
       </c>
       <c r="B31">
-        <v>4690</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46299.3125</v>
+        <v>46300.3125</v>
       </c>
       <c r="B32">
-        <v>4640</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46299.32291666666</v>
+        <v>46300.32291666666</v>
       </c>
       <c r="B33">
-        <v>4550</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46299.33333333334</v>
+        <v>46300.33333333334</v>
       </c>
       <c r="B34">
-        <v>4370</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46299.34375</v>
+        <v>46300.34375</v>
       </c>
       <c r="B35">
-        <v>4210</v>
+        <v>5770</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46299.35416666666</v>
+        <v>46300.35416666666</v>
       </c>
       <c r="B36">
-        <v>4060</v>
+        <v>5580</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46299.36458333334</v>
+        <v>46300.36458333334</v>
       </c>
       <c r="B37">
-        <v>3920</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46299.375</v>
+        <v>46300.375</v>
       </c>
       <c r="B38">
-        <v>3790</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46299.38541666666</v>
+        <v>46300.38541666666</v>
       </c>
       <c r="B39">
-        <v>3660</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46299.39583333334</v>
+        <v>46300.39583333334</v>
       </c>
       <c r="B40">
-        <v>3500</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46299.40625</v>
+        <v>46300.40625</v>
       </c>
       <c r="B41">
-        <v>3370</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46299.41666666666</v>
+        <v>46300.41666666666</v>
       </c>
       <c r="B42">
-        <v>3220</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46299.42708333334</v>
+        <v>46300.42708333334</v>
       </c>
       <c r="B43">
-        <v>3110</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46299.4375</v>
+        <v>46300.4375</v>
       </c>
       <c r="B44">
-        <v>3050</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46299.44791666666</v>
+        <v>46300.44791666666</v>
       </c>
       <c r="B45">
-        <v>3020</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46299.45833333334</v>
+        <v>46300.45833333334</v>
       </c>
       <c r="B46">
-        <v>3000</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46299.46875</v>
+        <v>46300.46875</v>
       </c>
       <c r="B47">
-        <v>2990</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46299.47916666666</v>
+        <v>46300.47916666666</v>
       </c>
       <c r="B48">
-        <v>2990</v>
+        <v>4190</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46299.48958333334</v>
+        <v>46300.48958333334</v>
       </c>
       <c r="B49">
-        <v>3020</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46299.5</v>
+        <v>46300.5</v>
       </c>
       <c r="B50">
-        <v>3050</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46299.51041666666</v>
+        <v>46300.51041666666</v>
       </c>
       <c r="B51">
-        <v>3080</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46299.52083333334</v>
+        <v>46300.52083333334</v>
       </c>
       <c r="B52">
-        <v>3110</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46299.53125</v>
+        <v>46300.53125</v>
       </c>
       <c r="B53">
-        <v>3160</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46299.54166666666</v>
+        <v>46300.54166666666</v>
       </c>
       <c r="B54">
-        <v>3210</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46299.55208333334</v>
+        <v>46300.55208333334</v>
       </c>
       <c r="B55">
-        <v>3270</v>
+        <v>4360</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46299.5625</v>
+        <v>46300.5625</v>
       </c>
       <c r="B56">
-        <v>3330</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46299.57291666666</v>
+        <v>46300.57291666666</v>
       </c>
       <c r="B57">
-        <v>3390</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46299.58333333334</v>
+        <v>46300.58333333334</v>
       </c>
       <c r="B58">
-        <v>3450</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46299.59375</v>
+        <v>46300.59375</v>
       </c>
       <c r="B59">
-        <v>3510</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46299.60416666666</v>
+        <v>46300.60416666666</v>
       </c>
       <c r="B60">
-        <v>3580</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46299.61458333334</v>
+        <v>46300.61458333334</v>
       </c>
       <c r="B61">
-        <v>3660</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46299.625</v>
+        <v>46300.625</v>
       </c>
       <c r="B62">
-        <v>3750</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46299.63541666666</v>
+        <v>46300.63541666666</v>
       </c>
       <c r="B63">
-        <v>3870</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46299.64583333334</v>
+        <v>46300.64583333334</v>
       </c>
       <c r="B64">
-        <v>4010</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46299.65625</v>
+        <v>46300.65625</v>
       </c>
       <c r="B65">
-        <v>4170</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46299.66666666666</v>
+        <v>46300.66666666666</v>
       </c>
       <c r="B66">
-        <v>4380</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46299.67708333334</v>
+        <v>46300.67708333334</v>
       </c>
       <c r="B67">
-        <v>4560</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46299.6875</v>
+        <v>46300.6875</v>
       </c>
       <c r="B68">
-        <v>4740</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46299.69791666666</v>
+        <v>46300.69791666666</v>
       </c>
       <c r="B69">
-        <v>4920</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46299.70833333334</v>
+        <v>46300.70833333334</v>
       </c>
       <c r="B70">
-        <v>5090</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46299.71875</v>
+        <v>46300.71875</v>
       </c>
       <c r="B71">
-        <v>5230</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46299.72916666666</v>
+        <v>46300.72916666666</v>
       </c>
       <c r="B72">
-        <v>5370</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46299.73958333334</v>
+        <v>46300.73958333334</v>
       </c>
       <c r="B73">
-        <v>5510</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46299.75</v>
+        <v>46300.75</v>
       </c>
       <c r="B74">
-        <v>5670</v>
+        <v>6590</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46299.76041666666</v>
+        <v>46300.76041666666</v>
       </c>
       <c r="B75">
-        <v>5810</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46299.77083333334</v>
+        <v>46300.77083333334</v>
       </c>
       <c r="B76">
-        <v>5920</v>
+        <v>6810</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46299.78125</v>
+        <v>46300.78125</v>
       </c>
       <c r="B77">
-        <v>6000</v>
+        <v>6910</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46299.79166666666</v>
+        <v>46300.79166666666</v>
       </c>
       <c r="B78">
-        <v>6050</v>
+        <v>7010</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46299.80208333334</v>
+        <v>46300.80208333334</v>
       </c>
       <c r="B79">
-        <v>6070</v>
+        <v>7050</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46299.8125</v>
+        <v>46300.8125</v>
       </c>
       <c r="B80">
-        <v>6060</v>
+        <v>7030</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46299.82291666666</v>
+        <v>46300.82291666666</v>
       </c>
       <c r="B81">
-        <v>6020</v>
+        <v>6940</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46299.83333333334</v>
+        <v>46300.83333333334</v>
       </c>
       <c r="B82">
-        <v>5900</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46299.84375</v>
+        <v>46300.84375</v>
       </c>
       <c r="B83">
-        <v>5750</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46299.85416666666</v>
+        <v>46300.85416666666</v>
       </c>
       <c r="B84">
-        <v>5620</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46299.86458333334</v>
+        <v>46300.86458333334</v>
       </c>
       <c r="B85">
-        <v>5530</v>
+        <v>6310</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46299.875</v>
+        <v>46300.875</v>
       </c>
       <c r="B86">
-        <v>5420</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46299.88541666666</v>
+        <v>46300.88541666666</v>
       </c>
       <c r="B87">
-        <v>5340</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46299.89583333334</v>
+        <v>46300.89583333334</v>
       </c>
       <c r="B88">
-        <v>5260</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46299.90625</v>
+        <v>46300.90625</v>
       </c>
       <c r="B89">
-        <v>5180</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46299.91666666666</v>
+        <v>46300.91666666666</v>
       </c>
       <c r="B90">
-        <v>5090</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46299.92708333334</v>
+        <v>46300.92708333334</v>
       </c>
       <c r="B91">
-        <v>5010</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46299.9375</v>
+        <v>46300.9375</v>
       </c>
       <c r="B92">
-        <v>4960</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46299.94791666666</v>
+        <v>46300.94791666666</v>
       </c>
       <c r="B93">
-        <v>4940</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46299.95833333334</v>
+        <v>46300.95833333334</v>
       </c>
       <c r="B94">
-        <v>4920</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46299.96875</v>
+        <v>46300.96875</v>
       </c>
       <c r="B95">
-        <v>4900</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46299.97916666666</v>
+        <v>46300.97916666666</v>
       </c>
       <c r="B96">
-        <v>4840</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46299.98958333334</v>
+        <v>46300.98958333334</v>
       </c>
       <c r="B97">
-        <v>4770</v>
+        <v>5530</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="B2">
-        <v>4720</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46300.01041666666</v>
+        <v>46307.01041666666</v>
       </c>
       <c r="B3">
-        <v>4680</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46300.02083333334</v>
+        <v>46307.02083333334</v>
       </c>
       <c r="B4">
-        <v>4650</v>
+        <v>4590</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46300.03125</v>
+        <v>46307.03125</v>
       </c>
       <c r="B5">
-        <v>4630</v>
+        <v>4570</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46300.04166666666</v>
+        <v>46307.04166666666</v>
       </c>
       <c r="B6">
-        <v>4610</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46300.05208333334</v>
+        <v>46307.05208333334</v>
       </c>
       <c r="B7">
-        <v>4600</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46300.0625</v>
+        <v>46307.0625</v>
       </c>
       <c r="B8">
-        <v>4600</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46300.07291666666</v>
+        <v>46307.07291666666</v>
       </c>
       <c r="B9">
-        <v>4610</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46300.08333333334</v>
+        <v>46307.08333333334</v>
       </c>
       <c r="B10">
-        <v>4630</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46300.09375</v>
+        <v>46307.09375</v>
       </c>
       <c r="B11">
-        <v>4650</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46300.10416666666</v>
+        <v>46307.10416666666</v>
       </c>
       <c r="B12">
-        <v>4690</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46300.11458333334</v>
+        <v>46307.11458333334</v>
       </c>
       <c r="B13">
-        <v>4720</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46300.125</v>
+        <v>46307.125</v>
       </c>
       <c r="B14">
-        <v>4750</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46300.13541666666</v>
+        <v>46307.13541666666</v>
       </c>
       <c r="B15">
-        <v>4790</v>
+        <v>4580</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46300.14583333334</v>
+        <v>46307.14583333334</v>
       </c>
       <c r="B16">
-        <v>4830</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46300.15625</v>
+        <v>46307.15625</v>
       </c>
       <c r="B17">
-        <v>4890</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46300.16666666666</v>
+        <v>46307.16666666666</v>
       </c>
       <c r="B18">
-        <v>4950</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46300.17708333334</v>
+        <v>46307.17708333334</v>
       </c>
       <c r="B19">
-        <v>5040</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46300.1875</v>
+        <v>46307.1875</v>
       </c>
       <c r="B20">
-        <v>5140</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46300.19791666666</v>
+        <v>46307.19791666666</v>
       </c>
       <c r="B21">
-        <v>5270</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46300.20833333334</v>
+        <v>46307.20833333334</v>
       </c>
       <c r="B22">
-        <v>5420</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46300.21875</v>
+        <v>46307.21875</v>
       </c>
       <c r="B23">
-        <v>5580</v>
+        <v>5450</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46300.22916666666</v>
+        <v>46307.22916666666</v>
       </c>
       <c r="B24">
-        <v>5750</v>
+        <v>5640</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46300.23958333334</v>
+        <v>46307.23958333334</v>
       </c>
       <c r="B25">
-        <v>5910</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46300.25</v>
+        <v>46307.25</v>
       </c>
       <c r="B26">
-        <v>6050</v>
+        <v>6070</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46300.26041666666</v>
+        <v>46307.26041666666</v>
       </c>
       <c r="B27">
-        <v>6180</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46300.27083333334</v>
+        <v>46307.27083333334</v>
       </c>
       <c r="B28">
-        <v>6270</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46300.28125</v>
+        <v>46307.28125</v>
       </c>
       <c r="B29">
-        <v>6300</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46300.29166666666</v>
+        <v>46307.29166666666</v>
       </c>
       <c r="B30">
-        <v>6290</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46300.30208333334</v>
+        <v>46307.30208333334</v>
       </c>
       <c r="B31">
-        <v>6270</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46300.3125</v>
+        <v>46307.3125</v>
       </c>
       <c r="B32">
-        <v>6210</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46300.32291666666</v>
+        <v>46307.32291666666</v>
       </c>
       <c r="B33">
-        <v>6090</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46300.33333333334</v>
+        <v>46307.33333333334</v>
       </c>
       <c r="B34">
-        <v>5940</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46300.34375</v>
+        <v>46307.34375</v>
       </c>
       <c r="B35">
-        <v>5770</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46300.35416666666</v>
+        <v>46307.35416666666</v>
       </c>
       <c r="B36">
-        <v>5580</v>
+        <v>6650</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46300.36458333334</v>
+        <v>46307.36458333334</v>
       </c>
       <c r="B37">
-        <v>5380</v>
+        <v>6610</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46300.375</v>
+        <v>46307.375</v>
       </c>
       <c r="B38">
-        <v>5190</v>
+        <v>6550</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46300.38541666666</v>
+        <v>46307.38541666666</v>
       </c>
       <c r="B39">
-        <v>5000</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46300.39583333334</v>
+        <v>46307.39583333334</v>
       </c>
       <c r="B40">
-        <v>4820</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46300.40625</v>
+        <v>46307.40625</v>
       </c>
       <c r="B41">
-        <v>4670</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46300.41666666666</v>
+        <v>46307.41666666666</v>
       </c>
       <c r="B42">
-        <v>4530</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46300.42708333334</v>
+        <v>46307.42708333334</v>
       </c>
       <c r="B43">
-        <v>4420</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46300.4375</v>
+        <v>46307.4375</v>
       </c>
       <c r="B44">
-        <v>4330</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46300.44791666666</v>
+        <v>46307.44791666666</v>
       </c>
       <c r="B45">
-        <v>4260</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46300.45833333334</v>
+        <v>46307.45833333334</v>
       </c>
       <c r="B46">
-        <v>4220</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46300.46875</v>
+        <v>46307.46875</v>
       </c>
       <c r="B47">
-        <v>4200</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46300.47916666666</v>
+        <v>46307.47916666666</v>
       </c>
       <c r="B48">
-        <v>4190</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46300.48958333334</v>
+        <v>46307.48958333334</v>
       </c>
       <c r="B49">
-        <v>4200</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46300.5</v>
+        <v>46307.5</v>
       </c>
       <c r="B50">
-        <v>4220</v>
+        <v>6110</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46300.51041666666</v>
+        <v>46307.51041666666</v>
       </c>
       <c r="B51">
-        <v>4240</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46300.52083333334</v>
+        <v>46307.52083333334</v>
       </c>
       <c r="B52">
-        <v>4260</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46300.53125</v>
+        <v>46307.53125</v>
       </c>
       <c r="B53">
-        <v>4290</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46300.54166666666</v>
+        <v>46307.54166666666</v>
       </c>
       <c r="B54">
-        <v>4320</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46300.55208333334</v>
+        <v>46307.55208333334</v>
       </c>
       <c r="B55">
-        <v>4360</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46300.5625</v>
+        <v>46307.5625</v>
       </c>
       <c r="B56">
-        <v>4400</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46300.57291666666</v>
+        <v>46307.57291666666</v>
       </c>
       <c r="B57">
-        <v>4460</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46300.58333333334</v>
+        <v>46307.58333333334</v>
       </c>
       <c r="B58">
-        <v>4520</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46300.59375</v>
+        <v>46307.59375</v>
       </c>
       <c r="B59">
-        <v>4600</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46300.60416666666</v>
+        <v>46307.60416666666</v>
       </c>
       <c r="B60">
-        <v>4700</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46300.61458333334</v>
+        <v>46307.61458333334</v>
       </c>
       <c r="B61">
-        <v>4800</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46300.625</v>
+        <v>46307.625</v>
       </c>
       <c r="B62">
-        <v>4920</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46300.63541666666</v>
+        <v>46307.63541666666</v>
       </c>
       <c r="B63">
-        <v>5050</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46300.64583333334</v>
+        <v>46307.64583333334</v>
       </c>
       <c r="B64">
-        <v>5180</v>
+        <v>6260</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46300.65625</v>
+        <v>46307.65625</v>
       </c>
       <c r="B65">
-        <v>5330</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46300.66666666666</v>
+        <v>46307.66666666666</v>
       </c>
       <c r="B66">
-        <v>5470</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46300.67708333334</v>
+        <v>46307.67708333334</v>
       </c>
       <c r="B67">
-        <v>5630</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46300.6875</v>
+        <v>46307.6875</v>
       </c>
       <c r="B68">
-        <v>5780</v>
+        <v>6520</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46300.69791666666</v>
+        <v>46307.69791666666</v>
       </c>
       <c r="B69">
-        <v>5940</v>
+        <v>6610</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46300.70833333334</v>
+        <v>46307.70833333334</v>
       </c>
       <c r="B70">
-        <v>6090</v>
+        <v>6710</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46300.71875</v>
+        <v>46307.71875</v>
       </c>
       <c r="B71">
-        <v>6230</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46300.72916666666</v>
+        <v>46307.72916666666</v>
       </c>
       <c r="B72">
-        <v>6360</v>
+        <v>6890</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46300.73958333334</v>
+        <v>46307.73958333334</v>
       </c>
       <c r="B73">
-        <v>6480</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46300.75</v>
+        <v>46307.75</v>
       </c>
       <c r="B74">
-        <v>6590</v>
+        <v>7110</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46300.76041666666</v>
+        <v>46307.76041666666</v>
       </c>
       <c r="B75">
-        <v>6700</v>
+        <v>7220</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46300.77083333334</v>
+        <v>46307.77083333334</v>
       </c>
       <c r="B76">
-        <v>6810</v>
+        <v>7270</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46300.78125</v>
+        <v>46307.78125</v>
       </c>
       <c r="B77">
-        <v>6910</v>
+        <v>7280</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46300.79166666666</v>
+        <v>46307.79166666666</v>
       </c>
       <c r="B78">
-        <v>7010</v>
+        <v>7270</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46300.80208333334</v>
+        <v>46307.80208333334</v>
       </c>
       <c r="B79">
-        <v>7050</v>
+        <v>7250</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46300.8125</v>
+        <v>46307.8125</v>
       </c>
       <c r="B80">
-        <v>7030</v>
+        <v>7180</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46300.82291666666</v>
+        <v>46307.82291666666</v>
       </c>
       <c r="B81">
-        <v>6940</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46300.83333333334</v>
+        <v>46307.83333333334</v>
       </c>
       <c r="B82">
-        <v>6720</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46300.84375</v>
+        <v>46307.84375</v>
       </c>
       <c r="B83">
-        <v>6480</v>
+        <v>6830</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46300.85416666666</v>
+        <v>46307.85416666666</v>
       </c>
       <c r="B84">
-        <v>6360</v>
+        <v>6710</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46300.86458333334</v>
+        <v>46307.86458333334</v>
       </c>
       <c r="B85">
-        <v>6310</v>
+        <v>6580</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46300.875</v>
+        <v>46307.875</v>
       </c>
       <c r="B86">
-        <v>6220</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46300.88541666666</v>
+        <v>46307.88541666666</v>
       </c>
       <c r="B87">
-        <v>6100</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46300.89583333334</v>
+        <v>46307.89583333334</v>
       </c>
       <c r="B88">
-        <v>5880</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46300.90625</v>
+        <v>46307.90625</v>
       </c>
       <c r="B89">
-        <v>5800</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46300.91666666666</v>
+        <v>46307.91666666666</v>
       </c>
       <c r="B90">
-        <v>5750</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46300.92708333334</v>
+        <v>46307.92708333334</v>
       </c>
       <c r="B91">
-        <v>5670</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46300.9375</v>
+        <v>46307.9375</v>
       </c>
       <c r="B92">
-        <v>5620</v>
+        <v>5680</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46300.94791666666</v>
+        <v>46307.94791666666</v>
       </c>
       <c r="B93">
-        <v>5530</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46300.95833333334</v>
+        <v>46307.95833333334</v>
       </c>
       <c r="B94">
-        <v>5530</v>
+        <v>5420</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46300.96875</v>
+        <v>46307.96875</v>
       </c>
       <c r="B95">
-        <v>5530</v>
+        <v>5360</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46300.97916666666</v>
+        <v>46307.97916666666</v>
       </c>
       <c r="B96">
-        <v>5530</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46300.98958333334</v>
+        <v>46307.98958333334</v>
       </c>
       <c r="B97">
-        <v>5530</v>
+        <v>5260</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,770 +394,770 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2">
-        <v>4650</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46307.01041666666</v>
+        <v>46308.01041666666</v>
       </c>
       <c r="B3">
-        <v>4610</v>
+        <v>5120</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46307.02083333334</v>
+        <v>46308.02083333334</v>
       </c>
       <c r="B4">
-        <v>4590</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46307.03125</v>
+        <v>46308.03125</v>
       </c>
       <c r="B5">
-        <v>4570</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46307.04166666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="B6">
-        <v>4530</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46307.05208333334</v>
+        <v>46308.05208333334</v>
       </c>
       <c r="B7">
-        <v>4520</v>
+        <v>5080</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46307.0625</v>
+        <v>46308.0625</v>
       </c>
       <c r="B8">
-        <v>4520</v>
+        <v>5090</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46307.07291666666</v>
+        <v>46308.07291666666</v>
       </c>
       <c r="B9">
-        <v>4520</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46307.08333333334</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="B10">
-        <v>4530</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46307.09375</v>
+        <v>46308.09375</v>
       </c>
       <c r="B11">
-        <v>4530</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46307.10416666666</v>
+        <v>46308.10416666666</v>
       </c>
       <c r="B12">
-        <v>4530</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46307.11458333334</v>
+        <v>46308.11458333334</v>
       </c>
       <c r="B13">
-        <v>4540</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46307.125</v>
+        <v>46308.125</v>
       </c>
       <c r="B14">
-        <v>4560</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46307.13541666666</v>
+        <v>46308.13541666666</v>
       </c>
       <c r="B15">
-        <v>4580</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46307.14583333334</v>
+        <v>46308.14583333334</v>
       </c>
       <c r="B16">
-        <v>4610</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46307.15625</v>
+        <v>46308.15625</v>
       </c>
       <c r="B17">
-        <v>4650</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46307.16666666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="B18">
-        <v>4700</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46307.17708333334</v>
+        <v>46308.17708333334</v>
       </c>
       <c r="B19">
-        <v>4790</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46307.1875</v>
+        <v>46308.1875</v>
       </c>
       <c r="B20">
-        <v>4920</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46307.19791666666</v>
+        <v>46308.19791666666</v>
       </c>
       <c r="B21">
-        <v>5070</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46307.20833333334</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="B22">
-        <v>5260</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46307.21875</v>
+        <v>46308.21875</v>
       </c>
       <c r="B23">
-        <v>5450</v>
+        <v>5650</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46307.22916666666</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="B24">
-        <v>5640</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46307.23958333334</v>
+        <v>46308.23958333334</v>
       </c>
       <c r="B25">
-        <v>5850</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="B26">
-        <v>6070</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46307.26041666666</v>
+        <v>46308.26041666666</v>
       </c>
       <c r="B27">
-        <v>6240</v>
+        <v>6290</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
       <c r="B28">
-        <v>6390</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46307.28125</v>
+        <v>46308.28125</v>
       </c>
       <c r="B29">
-        <v>6500</v>
+        <v>6570</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46307.29166666666</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="B30">
-        <v>6600</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46307.30208333334</v>
+        <v>46308.30208333334</v>
       </c>
       <c r="B31">
-        <v>6650</v>
+        <v>6780</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46307.3125</v>
+        <v>46308.3125</v>
       </c>
       <c r="B32">
-        <v>6670</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46307.32291666666</v>
+        <v>46308.32291666666</v>
       </c>
       <c r="B33">
-        <v>6680</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46307.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="B34">
-        <v>6680</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46307.34375</v>
+        <v>46308.34375</v>
       </c>
       <c r="B35">
-        <v>6670</v>
+        <v>6940</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46307.35416666666</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="B36">
-        <v>6650</v>
+        <v>6940</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46307.36458333334</v>
+        <v>46308.36458333334</v>
       </c>
       <c r="B37">
-        <v>6610</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46307.375</v>
+        <v>46308.375</v>
       </c>
       <c r="B38">
-        <v>6550</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46307.38541666666</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="B39">
-        <v>6500</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46307.39583333334</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="B40">
-        <v>6460</v>
+        <v>6790</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46307.40625</v>
+        <v>46308.40625</v>
       </c>
       <c r="B41">
-        <v>6410</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46307.41666666666</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="B42">
-        <v>6350</v>
+        <v>6660</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46307.42708333334</v>
+        <v>46308.42708333334</v>
       </c>
       <c r="B43">
-        <v>6290</v>
+        <v>6610</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46307.4375</v>
+        <v>46308.4375</v>
       </c>
       <c r="B44">
-        <v>6260</v>
+        <v>6570</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46307.44791666666</v>
+        <v>46308.44791666666</v>
       </c>
       <c r="B45">
-        <v>6220</v>
+        <v>6530</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46307.45833333334</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="B46">
-        <v>6180</v>
+        <v>6510</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46307.46875</v>
+        <v>46308.46875</v>
       </c>
       <c r="B47">
-        <v>6150</v>
+        <v>6490</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46307.47916666666</v>
+        <v>46308.47916666666</v>
       </c>
       <c r="B48">
-        <v>6140</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46307.48958333334</v>
+        <v>46308.48958333334</v>
       </c>
       <c r="B49">
-        <v>6130</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46307.5</v>
+        <v>46308.5</v>
       </c>
       <c r="B50">
-        <v>6110</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46307.51041666666</v>
+        <v>46308.51041666666</v>
       </c>
       <c r="B51">
-        <v>6100</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46307.52083333334</v>
+        <v>46308.52083333334</v>
       </c>
       <c r="B52">
-        <v>6090</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46307.53125</v>
+        <v>46308.53125</v>
       </c>
       <c r="B53">
-        <v>6100</v>
+        <v>6440</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46307.54166666666</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="B54">
-        <v>6100</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46307.55208333334</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="B55">
-        <v>6100</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46307.5625</v>
+        <v>46308.5625</v>
       </c>
       <c r="B56">
-        <v>6100</v>
+        <v>6420</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46307.57291666666</v>
+        <v>46308.57291666666</v>
       </c>
       <c r="B57">
-        <v>6100</v>
+        <v>6420</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46307.58333333334</v>
+        <v>46308.58333333334</v>
       </c>
       <c r="B58">
-        <v>6140</v>
+        <v>6410</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46307.59375</v>
+        <v>46308.59375</v>
       </c>
       <c r="B59">
-        <v>6150</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46307.60416666666</v>
+        <v>46308.60416666666</v>
       </c>
       <c r="B60">
-        <v>6150</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46307.61458333334</v>
+        <v>46308.61458333334</v>
       </c>
       <c r="B61">
-        <v>6160</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46307.625</v>
+        <v>46308.625</v>
       </c>
       <c r="B62">
-        <v>6190</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46307.63541666666</v>
+        <v>46308.63541666666</v>
       </c>
       <c r="B63">
-        <v>6230</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46307.64583333334</v>
+        <v>46308.64583333334</v>
       </c>
       <c r="B64">
-        <v>6260</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46307.65625</v>
+        <v>46308.65625</v>
       </c>
       <c r="B65">
-        <v>6320</v>
+        <v>6530</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46307.66666666666</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="B66">
-        <v>6390</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46307.67708333334</v>
+        <v>46308.67708333334</v>
       </c>
       <c r="B67">
-        <v>6460</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46307.6875</v>
+        <v>46308.6875</v>
       </c>
       <c r="B68">
-        <v>6520</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46307.69791666666</v>
+        <v>46308.69791666666</v>
       </c>
       <c r="B69">
-        <v>6610</v>
+        <v>6830</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46307.70833333334</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="B70">
-        <v>6710</v>
+        <v>6910</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46307.71875</v>
+        <v>46308.71875</v>
       </c>
       <c r="B71">
-        <v>6800</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46307.72916666666</v>
+        <v>46308.72916666666</v>
       </c>
       <c r="B72">
-        <v>6890</v>
+        <v>7090</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46307.73958333334</v>
+        <v>46308.73958333334</v>
       </c>
       <c r="B73">
-        <v>7000</v>
+        <v>7180</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46307.75</v>
+        <v>46308.75</v>
       </c>
       <c r="B74">
-        <v>7110</v>
+        <v>7260</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46307.76041666666</v>
+        <v>46308.76041666666</v>
       </c>
       <c r="B75">
-        <v>7220</v>
+        <v>7330</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46307.77083333334</v>
+        <v>46308.77083333334</v>
       </c>
       <c r="B76">
-        <v>7270</v>
+        <v>7370</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46307.78125</v>
+        <v>46308.78125</v>
       </c>
       <c r="B77">
-        <v>7280</v>
+        <v>7380</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46307.79166666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="B78">
-        <v>7270</v>
+        <v>7370</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46307.80208333334</v>
+        <v>46308.80208333334</v>
       </c>
       <c r="B79">
-        <v>7250</v>
+        <v>7340</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46307.8125</v>
+        <v>46308.8125</v>
       </c>
       <c r="B80">
-        <v>7180</v>
+        <v>7280</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46307.82291666666</v>
+        <v>46308.82291666666</v>
       </c>
       <c r="B81">
-        <v>7100</v>
+        <v>7180</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46307.83333333334</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="B82">
-        <v>6960</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46307.84375</v>
+        <v>46308.84375</v>
       </c>
       <c r="B83">
-        <v>6830</v>
+        <v>6970</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46307.85416666666</v>
+        <v>46308.85416666666</v>
       </c>
       <c r="B84">
-        <v>6710</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46307.86458333334</v>
+        <v>46308.86458333334</v>
       </c>
       <c r="B85">
-        <v>6580</v>
+        <v>6720</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46307.875</v>
+        <v>46308.875</v>
       </c>
       <c r="B86">
-        <v>6430</v>
+        <v>6570</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46307.88541666666</v>
+        <v>46308.88541666666</v>
       </c>
       <c r="B87">
-        <v>6300</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46307.89583333334</v>
+        <v>46308.89583333334</v>
       </c>
       <c r="B88">
-        <v>6150</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46307.90625</v>
+        <v>46308.90625</v>
       </c>
       <c r="B89">
-        <v>6020</v>
+        <v>6150</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46307.91666666666</v>
+        <v>46308.91666666666</v>
       </c>
       <c r="B90">
-        <v>5910</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46307.92708333334</v>
+        <v>46308.92708333334</v>
       </c>
       <c r="B91">
-        <v>5790</v>
+        <v>5880</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46307.9375</v>
+        <v>46308.9375</v>
       </c>
       <c r="B92">
-        <v>5680</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46307.94791666666</v>
+        <v>46308.94791666666</v>
       </c>
       <c r="B93">
-        <v>5570</v>
+        <v>5630</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46307.95833333334</v>
+        <v>46308.95833333334</v>
       </c>
       <c r="B94">
-        <v>5420</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46307.96875</v>
+        <v>46308.96875</v>
       </c>
       <c r="B95">
-        <v>5360</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46307.97916666666</v>
+        <v>46308.97916666666</v>
       </c>
       <c r="B96">
-        <v>5310</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46307.98958333334</v>
+        <v>46308.98958333334</v>
       </c>
       <c r="B97">
-        <v>5260</v>
+        <v>5170</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,727 +394,727 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="B2">
-        <v>5160</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46308.01041666666</v>
+        <v>46311.01041666666</v>
       </c>
       <c r="B3">
-        <v>5120</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46308.02083333334</v>
+        <v>46311.02083333334</v>
       </c>
       <c r="B4">
-        <v>5100</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46308.03125</v>
+        <v>46311.03125</v>
       </c>
       <c r="B5">
-        <v>5080</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46308.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="B6">
-        <v>5080</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46308.05208333334</v>
+        <v>46311.05208333334</v>
       </c>
       <c r="B7">
-        <v>5080</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46308.0625</v>
+        <v>46311.0625</v>
       </c>
       <c r="B8">
-        <v>5090</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46308.07291666666</v>
+        <v>46311.07291666666</v>
       </c>
       <c r="B9">
-        <v>5110</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46308.08333333334</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="B10">
-        <v>5130</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46308.09375</v>
+        <v>46311.09375</v>
       </c>
       <c r="B11">
-        <v>5150</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46308.10416666666</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="B12">
-        <v>5160</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46308.11458333334</v>
+        <v>46311.11458333334</v>
       </c>
       <c r="B13">
-        <v>5160</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46308.125</v>
+        <v>46311.125</v>
       </c>
       <c r="B14">
-        <v>5150</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46308.13541666666</v>
+        <v>46311.13541666666</v>
       </c>
       <c r="B15">
-        <v>5140</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46308.14583333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="B16">
-        <v>5130</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46308.15625</v>
+        <v>46311.15625</v>
       </c>
       <c r="B17">
-        <v>5130</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46308.16666666666</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="B18">
-        <v>5150</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46308.17708333334</v>
+        <v>46311.17708333334</v>
       </c>
       <c r="B19">
-        <v>5200</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46308.1875</v>
+        <v>46311.1875</v>
       </c>
       <c r="B20">
-        <v>5270</v>
+        <v>5370</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46308.19791666666</v>
+        <v>46311.19791666666</v>
       </c>
       <c r="B21">
-        <v>5380</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46308.20833333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="B22">
-        <v>5500</v>
+        <v>5650</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46308.21875</v>
+        <v>46311.21875</v>
       </c>
       <c r="B23">
-        <v>5650</v>
+        <v>5870</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46308.22916666666</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="B24">
-        <v>5810</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46308.23958333334</v>
+        <v>46311.23958333334</v>
       </c>
       <c r="B25">
-        <v>5970</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46308.25</v>
+        <v>46311.25</v>
       </c>
       <c r="B26">
-        <v>6140</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46308.26041666666</v>
+        <v>46311.26041666666</v>
       </c>
       <c r="B27">
-        <v>6290</v>
+        <v>6670</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46308.27083333334</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="B28">
-        <v>6440</v>
+        <v>6780</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46308.28125</v>
+        <v>46311.28125</v>
       </c>
       <c r="B29">
-        <v>6570</v>
+        <v>6870</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46308.29166666666</v>
+        <v>46311.29166666666</v>
       </c>
       <c r="B30">
-        <v>6680</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46308.30208333334</v>
+        <v>46311.30208333334</v>
       </c>
       <c r="B31">
-        <v>6780</v>
+        <v>6950</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46308.3125</v>
+        <v>46311.3125</v>
       </c>
       <c r="B32">
-        <v>6850</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46308.32291666666</v>
+        <v>46311.32291666666</v>
       </c>
       <c r="B33">
-        <v>6900</v>
+        <v>6940</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46308.33333333334</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="B34">
-        <v>6930</v>
+        <v>6890</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46308.34375</v>
+        <v>46311.34375</v>
       </c>
       <c r="B35">
-        <v>6940</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46308.35416666666</v>
+        <v>46311.35416666666</v>
       </c>
       <c r="B36">
-        <v>6940</v>
+        <v>6770</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46308.36458333334</v>
+        <v>46311.36458333334</v>
       </c>
       <c r="B37">
-        <v>6920</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46308.375</v>
+        <v>46311.375</v>
       </c>
       <c r="B38">
-        <v>6880</v>
+        <v>6620</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46308.38541666666</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="B39">
-        <v>6840</v>
+        <v>6540</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46308.39583333334</v>
+        <v>46311.39583333334</v>
       </c>
       <c r="B40">
-        <v>6790</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46308.40625</v>
+        <v>46311.40625</v>
       </c>
       <c r="B41">
-        <v>6720</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46308.41666666666</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="B42">
-        <v>6660</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46308.42708333334</v>
+        <v>46311.42708333334</v>
       </c>
       <c r="B43">
-        <v>6610</v>
+        <v>6230</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46308.4375</v>
+        <v>46311.4375</v>
       </c>
       <c r="B44">
-        <v>6570</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46308.44791666666</v>
+        <v>46311.44791666666</v>
       </c>
       <c r="B45">
-        <v>6530</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46308.45833333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="B46">
-        <v>6510</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46308.46875</v>
+        <v>46311.46875</v>
       </c>
       <c r="B47">
-        <v>6490</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46308.47916666666</v>
+        <v>46311.47916666666</v>
       </c>
       <c r="B48">
-        <v>6470</v>
+        <v>5990</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46308.48958333334</v>
+        <v>46311.48958333334</v>
       </c>
       <c r="B49">
-        <v>6450</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="B50">
-        <v>6440</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46308.51041666666</v>
+        <v>46311.51041666666</v>
       </c>
       <c r="B51">
-        <v>6440</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46308.52083333334</v>
+        <v>46311.52083333334</v>
       </c>
       <c r="B52">
-        <v>6440</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46308.53125</v>
+        <v>46311.53125</v>
       </c>
       <c r="B53">
-        <v>6440</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46308.54166666666</v>
+        <v>46311.54166666666</v>
       </c>
       <c r="B54">
-        <v>6430</v>
+        <v>5930</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46308.55208333334</v>
+        <v>46311.55208333334</v>
       </c>
       <c r="B55">
-        <v>6430</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46308.5625</v>
+        <v>46311.5625</v>
       </c>
       <c r="B56">
-        <v>6420</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46308.57291666666</v>
+        <v>46311.57291666666</v>
       </c>
       <c r="B57">
-        <v>6420</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46308.58333333334</v>
+        <v>46311.58333333334</v>
       </c>
       <c r="B58">
-        <v>6410</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46308.59375</v>
+        <v>46311.59375</v>
       </c>
       <c r="B59">
-        <v>6400</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46308.60416666666</v>
+        <v>46311.60416666666</v>
       </c>
       <c r="B60">
-        <v>6390</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46308.61458333334</v>
+        <v>46311.61458333334</v>
       </c>
       <c r="B61">
-        <v>6380</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46308.625</v>
+        <v>46311.625</v>
       </c>
       <c r="B62">
-        <v>6400</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46308.63541666666</v>
+        <v>46311.63541666666</v>
       </c>
       <c r="B63">
-        <v>6430</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46308.64583333334</v>
+        <v>46311.64583333334</v>
       </c>
       <c r="B64">
-        <v>6480</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46308.65625</v>
+        <v>46311.65625</v>
       </c>
       <c r="B65">
-        <v>6530</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46308.66666666666</v>
+        <v>46311.66666666666</v>
       </c>
       <c r="B66">
-        <v>6600</v>
+        <v>6280</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46308.67708333334</v>
+        <v>46311.67708333334</v>
       </c>
       <c r="B67">
-        <v>6670</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46308.6875</v>
+        <v>46311.6875</v>
       </c>
       <c r="B68">
-        <v>6750</v>
+        <v>6510</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46308.69791666666</v>
+        <v>46311.69791666666</v>
       </c>
       <c r="B69">
-        <v>6830</v>
+        <v>6620</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46308.70833333334</v>
+        <v>46311.70833333334</v>
       </c>
       <c r="B70">
-        <v>6910</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46308.71875</v>
+        <v>46311.71875</v>
       </c>
       <c r="B71">
-        <v>7000</v>
+        <v>6860</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46308.72916666666</v>
+        <v>46311.72916666666</v>
       </c>
       <c r="B72">
-        <v>7090</v>
+        <v>6970</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46308.73958333334</v>
+        <v>46311.73958333334</v>
       </c>
       <c r="B73">
-        <v>7180</v>
+        <v>7080</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46308.75</v>
+        <v>46311.75</v>
       </c>
       <c r="B74">
-        <v>7260</v>
+        <v>7170</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46308.76041666666</v>
+        <v>46311.76041666666</v>
       </c>
       <c r="B75">
-        <v>7330</v>
+        <v>7250</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46308.77083333334</v>
+        <v>46311.77083333334</v>
       </c>
       <c r="B76">
-        <v>7370</v>
+        <v>7280</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46308.78125</v>
+        <v>46311.78125</v>
       </c>
       <c r="B77">
-        <v>7380</v>
+        <v>7280</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46308.79166666666</v>
+        <v>46311.79166666666</v>
       </c>
       <c r="B78">
-        <v>7370</v>
+        <v>7270</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46308.80208333334</v>
+        <v>46311.80208333334</v>
       </c>
       <c r="B79">
-        <v>7340</v>
+        <v>7250</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46308.8125</v>
+        <v>46311.8125</v>
       </c>
       <c r="B80">
-        <v>7280</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46308.82291666666</v>
+        <v>46311.82291666666</v>
       </c>
       <c r="B81">
-        <v>7180</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46308.83333333334</v>
+        <v>46311.83333333334</v>
       </c>
       <c r="B82">
-        <v>7080</v>
+        <v>7040</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46308.84375</v>
+        <v>46311.84375</v>
       </c>
       <c r="B83">
-        <v>6970</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46308.85416666666</v>
+        <v>46311.85416666666</v>
       </c>
       <c r="B84">
-        <v>6850</v>
+        <v>6790</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46308.86458333334</v>
+        <v>46311.86458333334</v>
       </c>
       <c r="B85">
-        <v>6720</v>
+        <v>6640</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46308.875</v>
+        <v>46311.875</v>
       </c>
       <c r="B86">
-        <v>6570</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46308.88541666666</v>
+        <v>46311.88541666666</v>
       </c>
       <c r="B87">
-        <v>6450</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46308.89583333334</v>
+        <v>46311.89583333334</v>
       </c>
       <c r="B88">
-        <v>6300</v>
+        <v>6210</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46308.90625</v>
+        <v>46311.90625</v>
       </c>
       <c r="B89">
-        <v>6150</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46308.91666666666</v>
+        <v>46311.91666666666</v>
       </c>
       <c r="B90">
-        <v>6010</v>
+        <v>5960</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46308.92708333334</v>
+        <v>46311.92708333334</v>
       </c>
       <c r="B91">
-        <v>5880</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46308.9375</v>
+        <v>46311.9375</v>
       </c>
       <c r="B92">
         <v>5740</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46308.94791666666</v>
+        <v>46311.94791666666</v>
       </c>
       <c r="B93">
         <v>5630</v>
@@ -1130,34 +1130,34 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46308.95833333334</v>
+        <v>46311.95833333334</v>
       </c>
       <c r="B94">
-        <v>5340</v>
+        <v>5450</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46308.96875</v>
+        <v>46311.96875</v>
       </c>
       <c r="B95">
-        <v>5270</v>
+        <v>5380</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46308.97916666666</v>
+        <v>46311.97916666666</v>
       </c>
       <c r="B96">
-        <v>5210</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46308.98958333334</v>
+        <v>46311.98958333334</v>
       </c>
       <c r="B97">
-        <v>5170</v>
+        <v>5300</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -394,55 +394,55 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="B2">
-        <v>5280</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46311.01041666666</v>
+        <v>46316.01041666666</v>
       </c>
       <c r="B3">
-        <v>5260</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46311.02083333334</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="B4">
-        <v>5240</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46311.03125</v>
+        <v>46316.03125</v>
       </c>
       <c r="B5">
-        <v>5220</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46311.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="B6">
-        <v>5210</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46311.05208333334</v>
+        <v>46316.05208333334</v>
       </c>
       <c r="B7">
-        <v>5210</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46311.0625</v>
+        <v>46316.0625</v>
       </c>
       <c r="B8">
         <v>5230</v>
@@ -450,95 +450,95 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46311.07291666666</v>
+        <v>46316.07291666666</v>
       </c>
       <c r="B9">
-        <v>5240</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46311.08333333334</v>
+        <v>46316.08333333334</v>
       </c>
       <c r="B10">
-        <v>5310</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46311.09375</v>
+        <v>46316.09375</v>
       </c>
       <c r="B11">
-        <v>5330</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46311.10416666666</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="B12">
-        <v>5330</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46311.11458333334</v>
+        <v>46316.11458333334</v>
       </c>
       <c r="B13">
-        <v>5320</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46311.125</v>
+        <v>46316.125</v>
       </c>
       <c r="B14">
-        <v>5280</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46311.13541666666</v>
+        <v>46316.13541666666</v>
       </c>
       <c r="B15">
-        <v>5260</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46311.14583333334</v>
+        <v>46316.14583333334</v>
       </c>
       <c r="B16">
-        <v>5250</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46311.15625</v>
+        <v>46316.15625</v>
       </c>
       <c r="B17">
-        <v>5250</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46311.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="B18">
-        <v>5270</v>
+        <v>5230</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46311.17708333334</v>
+        <v>46316.17708333334</v>
       </c>
       <c r="B19">
-        <v>5310</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46311.1875</v>
+        <v>46316.1875</v>
       </c>
       <c r="B20">
         <v>5370</v>
@@ -546,103 +546,103 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46311.19791666666</v>
+        <v>46316.19791666666</v>
       </c>
       <c r="B21">
-        <v>5480</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46311.20833333334</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="B22">
-        <v>5650</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46311.21875</v>
+        <v>46316.21875</v>
       </c>
       <c r="B23">
-        <v>5870</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46311.22916666666</v>
+        <v>46316.22916666666</v>
       </c>
       <c r="B24">
-        <v>6060</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46311.23958333334</v>
+        <v>46316.23958333334</v>
       </c>
       <c r="B25">
-        <v>6280</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46311.25</v>
+        <v>46316.25</v>
       </c>
       <c r="B26">
-        <v>6500</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46311.26041666666</v>
+        <v>46316.26041666666</v>
       </c>
       <c r="B27">
-        <v>6670</v>
+        <v>6550</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46311.27083333334</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="B28">
-        <v>6780</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46311.28125</v>
+        <v>46316.28125</v>
       </c>
       <c r="B29">
-        <v>6870</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46311.29166666666</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="B30">
-        <v>6930</v>
+        <v>6920</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46311.30208333334</v>
+        <v>46316.30208333334</v>
       </c>
       <c r="B31">
-        <v>6950</v>
+        <v>6970</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46311.3125</v>
+        <v>46316.3125</v>
       </c>
       <c r="B32">
-        <v>6960</v>
+        <v>6970</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46311.32291666666</v>
+        <v>46316.32291666666</v>
       </c>
       <c r="B33">
         <v>6940</v>
@@ -650,383 +650,383 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46311.33333333334</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="B34">
-        <v>6890</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46311.34375</v>
+        <v>46316.34375</v>
       </c>
       <c r="B35">
-        <v>6840</v>
+        <v>6730</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46311.35416666666</v>
+        <v>46316.35416666666</v>
       </c>
       <c r="B36">
-        <v>6770</v>
+        <v>6610</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46311.36458333334</v>
+        <v>46316.36458333334</v>
       </c>
       <c r="B37">
-        <v>6700</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46311.375</v>
+        <v>46316.375</v>
       </c>
       <c r="B38">
-        <v>6620</v>
+        <v>6330</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46311.38541666666</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="B39">
-        <v>6540</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46311.39583333334</v>
+        <v>46316.39583333334</v>
       </c>
       <c r="B40">
-        <v>6460</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46311.40625</v>
+        <v>46316.40625</v>
       </c>
       <c r="B41">
-        <v>6380</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46311.41666666666</v>
+        <v>46316.41666666666</v>
       </c>
       <c r="B42">
-        <v>6300</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46311.42708333334</v>
+        <v>46316.42708333334</v>
       </c>
       <c r="B43">
-        <v>6230</v>
+        <v>5420</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46311.4375</v>
+        <v>46316.4375</v>
       </c>
       <c r="B44">
-        <v>6170</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46311.44791666666</v>
+        <v>46316.44791666666</v>
       </c>
       <c r="B45">
-        <v>6120</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46311.45833333334</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="B46">
-        <v>6060</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46311.46875</v>
+        <v>46316.46875</v>
       </c>
       <c r="B47">
-        <v>6020</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46311.47916666666</v>
+        <v>46316.47916666666</v>
       </c>
       <c r="B48">
-        <v>5990</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46311.48958333334</v>
+        <v>46316.48958333334</v>
       </c>
       <c r="B49">
-        <v>5960</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="B50">
-        <v>5950</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46311.51041666666</v>
+        <v>46316.51041666666</v>
       </c>
       <c r="B51">
-        <v>5940</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46311.52083333334</v>
+        <v>46316.52083333334</v>
       </c>
       <c r="B52">
-        <v>5940</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46311.53125</v>
+        <v>46316.53125</v>
       </c>
       <c r="B53">
-        <v>5940</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46311.54166666666</v>
+        <v>46316.54166666666</v>
       </c>
       <c r="B54">
-        <v>5930</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46311.55208333334</v>
+        <v>46316.55208333334</v>
       </c>
       <c r="B55">
-        <v>5920</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46311.5625</v>
+        <v>46316.5625</v>
       </c>
       <c r="B56">
-        <v>5920</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46311.57291666666</v>
+        <v>46316.57291666666</v>
       </c>
       <c r="B57">
-        <v>5910</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46311.58333333334</v>
+        <v>46316.58333333334</v>
       </c>
       <c r="B58">
-        <v>5900</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46311.59375</v>
+        <v>46316.59375</v>
       </c>
       <c r="B59">
-        <v>5900</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46311.60416666666</v>
+        <v>46316.60416666666</v>
       </c>
       <c r="B60">
-        <v>5910</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46311.61458333334</v>
+        <v>46316.61458333334</v>
       </c>
       <c r="B61">
-        <v>5920</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46311.625</v>
+        <v>46316.625</v>
       </c>
       <c r="B62">
-        <v>5950</v>
+        <v>5460</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46311.63541666666</v>
+        <v>46316.63541666666</v>
       </c>
       <c r="B63">
-        <v>6000</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46311.64583333334</v>
+        <v>46316.64583333334</v>
       </c>
       <c r="B64">
-        <v>6080</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46311.65625</v>
+        <v>46316.65625</v>
       </c>
       <c r="B65">
-        <v>6170</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46311.66666666666</v>
+        <v>46316.66666666666</v>
       </c>
       <c r="B66">
-        <v>6280</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46311.67708333334</v>
+        <v>46316.67708333334</v>
       </c>
       <c r="B67">
-        <v>6400</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46311.6875</v>
+        <v>46316.6875</v>
       </c>
       <c r="B68">
-        <v>6510</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46311.69791666666</v>
+        <v>46316.69791666666</v>
       </c>
       <c r="B69">
-        <v>6620</v>
+        <v>6560</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46311.70833333334</v>
+        <v>46316.70833333334</v>
       </c>
       <c r="B70">
-        <v>6750</v>
+        <v>6740</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46311.71875</v>
+        <v>46316.71875</v>
       </c>
       <c r="B71">
-        <v>6860</v>
+        <v>6890</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46311.72916666666</v>
+        <v>46316.72916666666</v>
       </c>
       <c r="B72">
-        <v>6970</v>
+        <v>7020</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46311.73958333334</v>
+        <v>46316.73958333334</v>
       </c>
       <c r="B73">
-        <v>7080</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46311.75</v>
+        <v>46316.75</v>
       </c>
       <c r="B74">
-        <v>7170</v>
+        <v>7250</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46311.76041666666</v>
+        <v>46316.76041666666</v>
       </c>
       <c r="B75">
-        <v>7250</v>
+        <v>7330</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46311.77083333334</v>
+        <v>46316.77083333334</v>
       </c>
       <c r="B76">
-        <v>7280</v>
+        <v>7370</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46311.78125</v>
+        <v>46316.78125</v>
       </c>
       <c r="B77">
-        <v>7280</v>
+        <v>7370</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46311.79166666666</v>
+        <v>46316.79166666666</v>
       </c>
       <c r="B78">
-        <v>7270</v>
+        <v>7330</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46311.80208333334</v>
+        <v>46316.80208333334</v>
       </c>
       <c r="B79">
-        <v>7250</v>
+        <v>7290</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46311.8125</v>
+        <v>46316.8125</v>
       </c>
       <c r="B80">
-        <v>7200</v>
+        <v>7230</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46311.82291666666</v>
+        <v>46316.82291666666</v>
       </c>
       <c r="B81">
         <v>7150</v>
@@ -1034,31 +1034,31 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46311.83333333334</v>
+        <v>46316.83333333334</v>
       </c>
       <c r="B82">
-        <v>7040</v>
+        <v>7020</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46311.84375</v>
+        <v>46316.84375</v>
       </c>
       <c r="B83">
-        <v>6920</v>
+        <v>6890</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46311.85416666666</v>
+        <v>46316.85416666666</v>
       </c>
       <c r="B84">
-        <v>6790</v>
+        <v>6770</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46311.86458333334</v>
+        <v>46316.86458333334</v>
       </c>
       <c r="B85">
         <v>6640</v>
@@ -1066,55 +1066,55 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46311.875</v>
+        <v>46316.875</v>
       </c>
       <c r="B86">
-        <v>6480</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46311.88541666666</v>
+        <v>46316.88541666666</v>
       </c>
       <c r="B87">
-        <v>6350</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46311.89583333334</v>
+        <v>46316.89583333334</v>
       </c>
       <c r="B88">
-        <v>6210</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46311.90625</v>
+        <v>46316.90625</v>
       </c>
       <c r="B89">
-        <v>6090</v>
+        <v>6060</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46311.91666666666</v>
+        <v>46316.91666666666</v>
       </c>
       <c r="B90">
-        <v>5960</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46311.92708333334</v>
+        <v>46316.92708333334</v>
       </c>
       <c r="B91">
-        <v>5840</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46311.9375</v>
+        <v>46316.9375</v>
       </c>
       <c r="B92">
         <v>5740</v>
@@ -1122,42 +1122,42 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46311.94791666666</v>
+        <v>46316.94791666666</v>
       </c>
       <c r="B93">
-        <v>5630</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46311.95833333334</v>
+        <v>46316.95833333334</v>
       </c>
       <c r="B94">
-        <v>5450</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46311.96875</v>
+        <v>46316.96875</v>
       </c>
       <c r="B95">
-        <v>5380</v>
+        <v>5440</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46311.97916666666</v>
+        <v>46316.97916666666</v>
       </c>
       <c r="B96">
-        <v>5340</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46311.98958333334</v>
+        <v>46316.98958333334</v>
       </c>
       <c r="B97">
-        <v>5300</v>
+        <v>5340</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Consumption_Forecast.xlsx
+++ b/data_fetching/Entsoe/Consumption_Forecast.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,770 +394,802 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="B2">
-        <v>5330</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46316.01041666666</v>
+        <v>46320.01041666666</v>
       </c>
       <c r="B3">
-        <v>5330</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46316.02083333334</v>
+        <v>46320.02083333334</v>
       </c>
       <c r="B4">
-        <v>5320</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46316.03125</v>
+        <v>46320.03125</v>
       </c>
       <c r="B5">
-        <v>5310</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46316.04166666666</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="B6">
-        <v>5280</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46316.05208333334</v>
+        <v>46320.05208333334</v>
       </c>
       <c r="B7">
-        <v>5250</v>
+        <v>4730</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46316.0625</v>
+        <v>46320.0625</v>
       </c>
       <c r="B8">
-        <v>5230</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46316.07291666666</v>
+        <v>46320.07291666666</v>
       </c>
       <c r="B9">
-        <v>5220</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46316.08333333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B10">
-        <v>5200</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46316.09375</v>
+        <v>46320.09375</v>
       </c>
       <c r="B11">
-        <v>5200</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46316.10416666666</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B12">
-        <v>5200</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46316.11458333334</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B13">
-        <v>5210</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46316.125</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B14">
-        <v>5230</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46316.13541666666</v>
+        <v>46320.09375</v>
       </c>
       <c r="B15">
-        <v>5230</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46316.14583333334</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B16">
-        <v>5230</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46316.15625</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B17">
-        <v>5230</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46316.16666666666</v>
+        <v>46320.125</v>
       </c>
       <c r="B18">
-        <v>5230</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46316.17708333334</v>
+        <v>46320.13541666666</v>
       </c>
       <c r="B19">
-        <v>5290</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46316.1875</v>
+        <v>46320.14583333334</v>
       </c>
       <c r="B20">
-        <v>5370</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46316.19791666666</v>
+        <v>46320.15625</v>
       </c>
       <c r="B21">
-        <v>5470</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46316.20833333334</v>
+        <v>46320.16666666666</v>
       </c>
       <c r="B22">
-        <v>5620</v>
+        <v>4660</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46316.21875</v>
+        <v>46320.17708333334</v>
       </c>
       <c r="B23">
-        <v>5780</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46316.22916666666</v>
+        <v>46320.1875</v>
       </c>
       <c r="B24">
-        <v>5950</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46316.23958333334</v>
+        <v>46320.19791666666</v>
       </c>
       <c r="B25">
-        <v>6130</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46316.25</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="B26">
-        <v>6370</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46316.26041666666</v>
+        <v>46320.21875</v>
       </c>
       <c r="B27">
-        <v>6550</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46316.27083333334</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="B28">
-        <v>6680</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46316.28125</v>
+        <v>46320.23958333334</v>
       </c>
       <c r="B29">
-        <v>6800</v>
+        <v>4960</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46316.29166666666</v>
+        <v>46320.25</v>
       </c>
       <c r="B30">
-        <v>6920</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46316.30208333334</v>
+        <v>46320.26041666666</v>
       </c>
       <c r="B31">
-        <v>6970</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46316.3125</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="B32">
-        <v>6970</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46316.32291666666</v>
+        <v>46320.28125</v>
       </c>
       <c r="B33">
-        <v>6940</v>
+        <v>5160</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46316.33333333334</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="B34">
-        <v>6840</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46316.34375</v>
+        <v>46320.30208333334</v>
       </c>
       <c r="B35">
-        <v>6730</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46316.35416666666</v>
+        <v>46320.3125</v>
       </c>
       <c r="B36">
-        <v>6610</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46316.36458333334</v>
+        <v>46320.32291666666</v>
       </c>
       <c r="B37">
-        <v>6470</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46316.375</v>
+        <v>46320.33333333334</v>
       </c>
       <c r="B38">
-        <v>6330</v>
+        <v>5210</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46316.38541666666</v>
+        <v>46320.34375</v>
       </c>
       <c r="B39">
-        <v>6170</v>
+        <v>5180</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46316.39583333334</v>
+        <v>46320.35416666666</v>
       </c>
       <c r="B40">
-        <v>5980</v>
+        <v>5150</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46316.40625</v>
+        <v>46320.36458333334</v>
       </c>
       <c r="B41">
-        <v>5800</v>
+        <v>5100</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46316.41666666666</v>
+        <v>46320.375</v>
       </c>
       <c r="B42">
-        <v>5590</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46316.42708333334</v>
+        <v>46320.38541666666</v>
       </c>
       <c r="B43">
-        <v>5420</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46316.4375</v>
+        <v>46320.39583333334</v>
       </c>
       <c r="B44">
-        <v>5260</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46316.44791666666</v>
+        <v>46320.40625</v>
       </c>
       <c r="B45">
-        <v>5140</v>
+        <v>4860</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46316.45833333334</v>
+        <v>46320.41666666666</v>
       </c>
       <c r="B46">
-        <v>5020</v>
+        <v>4810</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46316.46875</v>
+        <v>46320.42708333334</v>
       </c>
       <c r="B47">
-        <v>4940</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46316.47916666666</v>
+        <v>46320.4375</v>
       </c>
       <c r="B48">
-        <v>4920</v>
+        <v>4720</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46316.48958333334</v>
+        <v>46320.44791666666</v>
       </c>
       <c r="B49">
-        <v>4940</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46316.5</v>
+        <v>46320.45833333334</v>
       </c>
       <c r="B50">
-        <v>4960</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46316.51041666666</v>
+        <v>46320.46875</v>
       </c>
       <c r="B51">
-        <v>4980</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46316.52083333334</v>
+        <v>46320.47916666666</v>
       </c>
       <c r="B52">
-        <v>4990</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46316.53125</v>
+        <v>46320.48958333334</v>
       </c>
       <c r="B53">
-        <v>4990</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46316.54166666666</v>
+        <v>46320.5</v>
       </c>
       <c r="B54">
-        <v>5020</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46316.55208333334</v>
+        <v>46320.51041666666</v>
       </c>
       <c r="B55">
-        <v>5030</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46316.5625</v>
+        <v>46320.52083333334</v>
       </c>
       <c r="B56">
-        <v>5030</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46316.57291666666</v>
+        <v>46320.53125</v>
       </c>
       <c r="B57">
-        <v>5040</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46316.58333333334</v>
+        <v>46320.54166666666</v>
       </c>
       <c r="B58">
-        <v>5100</v>
+        <v>4660</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46316.59375</v>
+        <v>46320.55208333334</v>
       </c>
       <c r="B59">
-        <v>5150</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46316.60416666666</v>
+        <v>46320.5625</v>
       </c>
       <c r="B60">
-        <v>5220</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46316.61458333334</v>
+        <v>46320.57291666666</v>
       </c>
       <c r="B61">
-        <v>5330</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46316.625</v>
+        <v>46320.58333333334</v>
       </c>
       <c r="B62">
-        <v>5460</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46316.63541666666</v>
+        <v>46320.59375</v>
       </c>
       <c r="B63">
-        <v>5600</v>
+        <v>4990</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46316.64583333334</v>
+        <v>46320.60416666666</v>
       </c>
       <c r="B64">
-        <v>5750</v>
+        <v>5070</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46316.65625</v>
+        <v>46320.61458333334</v>
       </c>
       <c r="B65">
-        <v>5920</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46316.66666666666</v>
+        <v>46320.625</v>
       </c>
       <c r="B66">
-        <v>6090</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46316.67708333334</v>
+        <v>46320.63541666666</v>
       </c>
       <c r="B67">
-        <v>6250</v>
+        <v>5420</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46316.6875</v>
+        <v>46320.64583333334</v>
       </c>
       <c r="B68">
-        <v>6400</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46316.69791666666</v>
+        <v>46320.65625</v>
       </c>
       <c r="B69">
-        <v>6560</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46316.70833333334</v>
+        <v>46320.66666666666</v>
       </c>
       <c r="B70">
-        <v>6740</v>
+        <v>5860</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46316.71875</v>
+        <v>46320.67708333334</v>
       </c>
       <c r="B71">
-        <v>6890</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46316.72916666666</v>
+        <v>46320.6875</v>
       </c>
       <c r="B72">
-        <v>7020</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46316.73958333334</v>
+        <v>46320.69791666666</v>
       </c>
       <c r="B73">
-        <v>7150</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46316.75</v>
+        <v>46320.70833333334</v>
       </c>
       <c r="B74">
-        <v>7250</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46316.76041666666</v>
+        <v>46320.71875</v>
       </c>
       <c r="B75">
-        <v>7330</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46316.77083333334</v>
+        <v>46320.72916666666</v>
       </c>
       <c r="B76">
-        <v>7370</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46316.78125</v>
+        <v>46320.73958333334</v>
       </c>
       <c r="B77">
-        <v>7370</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46316.79166666666</v>
+        <v>46320.75</v>
       </c>
       <c r="B78">
-        <v>7330</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46316.80208333334</v>
+        <v>46320.76041666666</v>
       </c>
       <c r="B79">
-        <v>7290</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46316.8125</v>
+        <v>46320.77083333334</v>
       </c>
       <c r="B80">
-        <v>7230</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46316.82291666666</v>
+        <v>46320.78125</v>
       </c>
       <c r="B81">
-        <v>7150</v>
+        <v>6320</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46316.83333333334</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="B82">
-        <v>7020</v>
+        <v>6270</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46316.84375</v>
+        <v>46320.80208333334</v>
       </c>
       <c r="B83">
-        <v>6890</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46316.85416666666</v>
+        <v>46320.8125</v>
       </c>
       <c r="B84">
-        <v>6770</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46316.86458333334</v>
+        <v>46320.82291666666</v>
       </c>
       <c r="B85">
-        <v>6640</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46316.875</v>
+        <v>46320.83333333334</v>
       </c>
       <c r="B86">
-        <v>6470</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46316.88541666666</v>
+        <v>46320.84375</v>
       </c>
       <c r="B87">
-        <v>6320</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46316.89583333334</v>
+        <v>46320.85416666666</v>
       </c>
       <c r="B88">
-        <v>6170</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46316.90625</v>
+        <v>46320.86458333334</v>
       </c>
       <c r="B89">
-        <v>6060</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46316.91666666666</v>
+        <v>46320.875</v>
       </c>
       <c r="B90">
-        <v>5970</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46316.92708333334</v>
+        <v>46320.88541666666</v>
       </c>
       <c r="B91">
-        <v>5860</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46316.9375</v>
+        <v>46320.89583333334</v>
       </c>
       <c r="B92">
-        <v>5740</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46316.94791666666</v>
+        <v>46320.90625</v>
       </c>
       <c r="B93">
-        <v>5620</v>
+        <v>5310</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46316.95833333334</v>
+        <v>46320.91666666666</v>
       </c>
       <c r="B94">
-        <v>5500</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46316.96875</v>
+        <v>46320.92708333334</v>
       </c>
       <c r="B95">
-        <v>5440</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46316.97916666666</v>
+        <v>46320.9375</v>
       </c>
       <c r="B96">
-        <v>5390</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46316.98958333334</v>
+        <v>46320.94791666666</v>
       </c>
       <c r="B97">
-        <v>5340</v>
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
+        <v>46320.95833333334</v>
+      </c>
+      <c r="B98">
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46320.96875</v>
+      </c>
+      <c r="B99">
+        <v>4950</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46320.97916666666</v>
+      </c>
+      <c r="B100">
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46320.98958333334</v>
+      </c>
+      <c r="B101">
+        <v>4830</v>
       </c>
     </row>
   </sheetData>
